--- a/results/05_loo_validation/step4b_loo_validation_summary.xlsx
+++ b/results/05_loo_validation/step4b_loo_validation_summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">panel_id</t>
   </si>
@@ -90,25 +90,25 @@
     <t xml:space="preserve">LOO_P1_macroregion</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/02_snp_panels/panels/P1_macroregion_africa_vs_asia</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/02_snp_panels/panels/P1_macroregion_africa_vs_asia</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_predictions.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_predictions.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_raw.tsv.gz</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_raw.tsv.gz</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_summary.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_summary.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_perclass.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_perclass.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_confusion.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P1_macroregion_loo_confusion.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/FIG_LOO_P1_macroregion_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/FIG_LOO_P1_macroregion_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">P2_subregion_within_africa</t>
@@ -120,25 +120,25 @@
     <t xml:space="preserve">LOO_P2_africa_subregion</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/02_snp_panels/panels/P2_subregion_within_africa</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/02_snp_panels/panels/P2_subregion_within_africa</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_predictions.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_predictions.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_raw.tsv.gz</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_raw.tsv.gz</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_summary.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_summary.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_perclass.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_perclass.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_confusion.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P2_africa_subregion_loo_confusion.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/FIG_LOO_P2_africa_subregion_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/FIG_LOO_P2_africa_subregion_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">P3_subregion_within_asia</t>
@@ -147,25 +147,25 @@
     <t xml:space="preserve">LOO_P3_asia_subregion</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/02_snp_panels/panels/P3_subregion_within_asia</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/02_snp_panels/panels/P3_subregion_within_asia</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_predictions.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_predictions.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_raw.tsv.gz</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_raw.tsv.gz</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_summary.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_summary.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_perclass.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_perclass.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_confusion.tsv</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/LOO_P3_asia_subregion_loo_confusion.tsv</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation/FIG_LOO_P3_asia_subregion_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation/FIG_LOO_P3_asia_subregion_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
@@ -1260,6 +1260,15 @@
     <t xml:space="preserve">W_Africa</t>
   </si>
   <si>
+    <t xml:space="preserve">low_posterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low_gap</t>
+  </si>
+  <si>
     <t xml:space="preserve">S_Africa</t>
   </si>
   <si>
@@ -1270,12 +1279,6 @@
   </si>
   <si>
     <t xml:space="preserve">E_Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low_posterior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
@@ -1296,19 +1299,19 @@
     <t xml:space="preserve">qc_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/01_qc</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/01_qc</t>
   </si>
   <si>
     <t xml:space="preserve">step3_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/02_snp_panels</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/02_snp_panels</t>
   </si>
   <si>
     <t xml:space="preserve">out_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/05_loo_validation</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/05_loo_validation</t>
   </si>
   <si>
     <t xml:space="preserve">panels</t>
@@ -2079,16 +2082,16 @@
         <v>0.25</v>
       </c>
       <c r="K3" t="n">
-        <v>0.971428571428571</v>
+        <v>0.980952380952381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.971428571428571</v>
+        <v>0.980952380952381</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0761904761904762</v>
+        <v>0.0952380952380952</v>
       </c>
       <c r="N3" t="n">
-        <v>0.923809523809524</v>
+        <v>0.904761904761905</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -2141,10 +2144,10 @@
         <v>0.25</v>
       </c>
       <c r="K4" t="n">
-        <v>0.92093023255814</v>
+        <v>0.925581395348837</v>
       </c>
       <c r="L4" t="n">
-        <v>0.92093023255814</v>
+        <v>0.925581395348837</v>
       </c>
       <c r="M4" t="n">
         <v>0.0697674418604651</v>
@@ -2317,43 +2320,43 @@
         <v>105</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.971428571428571</v>
+        <v>0.980952380952381</v>
       </c>
       <c r="G3" t="n">
-        <v>0.971428571428571</v>
+        <v>0.980952380952381</v>
       </c>
       <c r="H3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0.923809523809524</v>
+        <v>0.904761904761905</v>
       </c>
       <c r="L3" t="n">
-        <v>0.923809523809524</v>
+        <v>0.904761904761905</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0761904761904762</v>
+        <v>0.0952380952380952</v>
       </c>
       <c r="N3" t="n">
-        <v>0.999888725992405</v>
+        <v>0.995498608265769</v>
       </c>
       <c r="O3" t="n">
-        <v>0.999777451984809</v>
+        <v>0.990997216531537</v>
       </c>
       <c r="P3" t="n">
-        <v>0.974603174603175</v>
+        <v>0.96984126984127</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.993650793650794</v>
+        <v>0.996825396825397</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -2376,13 +2379,13 @@
         <v>215</v>
       </c>
       <c r="E4" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F4" t="n">
-        <v>0.92093023255814</v>
+        <v>0.925581395348837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.92093023255814</v>
+        <v>0.925581395348837</v>
       </c>
       <c r="H4" t="n">
         <v>200</v>
@@ -2403,16 +2406,16 @@
         <v>0.0697674418604651</v>
       </c>
       <c r="N4" t="n">
-        <v>0.99827444874281</v>
+        <v>0.999855523383849</v>
       </c>
       <c r="O4" t="n">
-        <v>0.99654889748562</v>
+        <v>0.999711046767698</v>
       </c>
       <c r="P4" t="n">
-        <v>0.968992248062015</v>
+        <v>0.972868217054264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.990697674418605</v>
+        <v>0.993798449612403</v>
       </c>
       <c r="R4" t="n">
         <v>0.00930232558139535</v>
@@ -2556,7 +2559,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>11076</v>
+        <v>11077</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -2926,7 +2929,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="n">
-        <v>10935</v>
+        <v>10934</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -3000,7 +3003,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="n">
-        <v>11013</v>
+        <v>11014</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -3074,7 +3077,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="n">
-        <v>11053</v>
+        <v>11052</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -3296,7 +3299,7 @@
         <v>86</v>
       </c>
       <c r="P12" t="n">
-        <v>10859</v>
+        <v>10860</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -3444,7 +3447,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="n">
-        <v>10925</v>
+        <v>10926</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -3740,7 +3743,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="n">
-        <v>10999</v>
+        <v>11000</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -3962,7 +3965,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="n">
-        <v>11056</v>
+        <v>11055</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -4110,7 +4113,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="n">
-        <v>11025</v>
+        <v>11026</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -4554,7 +4557,7 @@
         <v>86</v>
       </c>
       <c r="P29" t="n">
-        <v>10952</v>
+        <v>10949</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
@@ -4628,7 +4631,7 @@
         <v>86</v>
       </c>
       <c r="P30" t="n">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -4998,7 +5001,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="n">
-        <v>11069</v>
+        <v>11068</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -5072,7 +5075,7 @@
         <v>86</v>
       </c>
       <c r="P36" t="n">
-        <v>11040</v>
+        <v>11041</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -6552,7 +6555,7 @@
         <v>86</v>
       </c>
       <c r="P56" t="n">
-        <v>10200</v>
+        <v>10202</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
@@ -6996,7 +6999,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="n">
-        <v>10986</v>
+        <v>10987</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -7144,7 +7147,7 @@
         <v>86</v>
       </c>
       <c r="P64" t="n">
-        <v>11035</v>
+        <v>11034</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
@@ -7292,7 +7295,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="n">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
@@ -7366,7 +7369,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="n">
-        <v>10994</v>
+        <v>10996</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
@@ -7440,7 +7443,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="n">
-        <v>11025</v>
+        <v>11026</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
@@ -7810,7 +7813,7 @@
         <v>86</v>
       </c>
       <c r="P73" t="n">
-        <v>11057</v>
+        <v>11056</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
@@ -7958,7 +7961,7 @@
         <v>86</v>
       </c>
       <c r="P75" t="n">
-        <v>11043</v>
+        <v>11044</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
@@ -8032,7 +8035,7 @@
         <v>86</v>
       </c>
       <c r="P76" t="n">
-        <v>11040</v>
+        <v>11039</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
@@ -8106,7 +8109,7 @@
         <v>86</v>
       </c>
       <c r="P77" t="n">
-        <v>10873</v>
+        <v>10874</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
@@ -8328,7 +8331,7 @@
         <v>86</v>
       </c>
       <c r="P80" t="n">
-        <v>11068</v>
+        <v>11069</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -9290,7 +9293,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="n">
-        <v>11020</v>
+        <v>11021</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
@@ -9438,7 +9441,7 @@
         <v>86</v>
       </c>
       <c r="P95" t="n">
-        <v>11036</v>
+        <v>11035</v>
       </c>
       <c r="Q95" t="n">
         <v>1</v>
@@ -9660,7 +9663,7 @@
         <v>86</v>
       </c>
       <c r="P98" t="n">
-        <v>11059</v>
+        <v>11058</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
@@ -10252,7 +10255,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="n">
-        <v>11064</v>
+        <v>11063</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
@@ -10992,7 +10995,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="n">
-        <v>11077</v>
+        <v>11076</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -11362,7 +11365,7 @@
         <v>86</v>
       </c>
       <c r="P121" t="n">
-        <v>11024</v>
+        <v>11023</v>
       </c>
       <c r="Q121" t="n">
         <v>1</v>
@@ -12102,7 +12105,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="n">
-        <v>11077</v>
+        <v>11076</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
@@ -12620,7 +12623,7 @@
         <v>86</v>
       </c>
       <c r="P138" t="n">
-        <v>11058</v>
+        <v>11057</v>
       </c>
       <c r="Q138" t="n">
         <v>1</v>
@@ -12694,7 +12697,7 @@
         <v>86</v>
       </c>
       <c r="P139" t="n">
-        <v>11068</v>
+        <v>11067</v>
       </c>
       <c r="Q139" t="n">
         <v>1</v>
@@ -13434,7 +13437,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="n">
-        <v>11067</v>
+        <v>11068</v>
       </c>
       <c r="Q149" t="n">
         <v>1</v>
@@ -13804,7 +13807,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="n">
-        <v>11046</v>
+        <v>11047</v>
       </c>
       <c r="Q154" t="n">
         <v>1</v>
@@ -13952,7 +13955,7 @@
         <v>86</v>
       </c>
       <c r="P156" t="n">
-        <v>11078</v>
+        <v>11079</v>
       </c>
       <c r="Q156" t="n">
         <v>1</v>
@@ -14026,7 +14029,7 @@
         <v>86</v>
       </c>
       <c r="P157" t="n">
-        <v>11053</v>
+        <v>11052</v>
       </c>
       <c r="Q157" t="n">
         <v>1</v>
@@ -14692,7 +14695,7 @@
         <v>86</v>
       </c>
       <c r="P166" t="n">
-        <v>11057</v>
+        <v>11058</v>
       </c>
       <c r="Q166" t="n">
         <v>1</v>
@@ -14766,7 +14769,7 @@
         <v>86</v>
       </c>
       <c r="P167" t="n">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="Q167" t="n">
         <v>1</v>
@@ -15506,7 +15509,7 @@
         <v>86</v>
       </c>
       <c r="P177" t="n">
-        <v>11071</v>
+        <v>11070</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
@@ -15728,7 +15731,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="n">
-        <v>11078</v>
+        <v>11077</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
@@ -15950,7 +15953,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
       <c r="Q183" t="n">
         <v>1</v>
@@ -16616,7 +16619,7 @@
         <v>86</v>
       </c>
       <c r="P192" t="n">
-        <v>11029</v>
+        <v>11030</v>
       </c>
       <c r="Q192" t="n">
         <v>1</v>
@@ -16764,7 +16767,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="n">
-        <v>11027</v>
+        <v>11028</v>
       </c>
       <c r="Q194" t="n">
         <v>1</v>
@@ -17060,7 +17063,7 @@
         <v>86</v>
       </c>
       <c r="P198" t="n">
-        <v>11050</v>
+        <v>11049</v>
       </c>
       <c r="Q198" t="n">
         <v>1</v>
@@ -17134,7 +17137,7 @@
         <v>86</v>
       </c>
       <c r="P199" t="n">
-        <v>11064</v>
+        <v>11065</v>
       </c>
       <c r="Q199" t="n">
         <v>1</v>
@@ -17356,7 +17359,7 @@
         <v>86</v>
       </c>
       <c r="P202" t="n">
-        <v>11067</v>
+        <v>11066</v>
       </c>
       <c r="Q202" t="n">
         <v>1</v>
@@ -17504,7 +17507,7 @@
         <v>86</v>
       </c>
       <c r="P204" t="n">
-        <v>11020</v>
+        <v>11019</v>
       </c>
       <c r="Q204" t="n">
         <v>1</v>
@@ -17578,7 +17581,7 @@
         <v>86</v>
       </c>
       <c r="P205" t="n">
-        <v>7497</v>
+        <v>7500</v>
       </c>
       <c r="Q205" t="n">
         <v>1</v>
@@ -17652,7 +17655,7 @@
         <v>86</v>
       </c>
       <c r="P206" t="n">
-        <v>10904</v>
+        <v>10903</v>
       </c>
       <c r="Q206" t="n">
         <v>1</v>
@@ -17874,7 +17877,7 @@
         <v>86</v>
       </c>
       <c r="P209" t="n">
-        <v>11030</v>
+        <v>11031</v>
       </c>
       <c r="Q209" t="n">
         <v>1</v>
@@ -18318,7 +18321,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="n">
-        <v>11021</v>
+        <v>11022</v>
       </c>
       <c r="Q215" t="n">
         <v>1</v>
@@ -18392,7 +18395,7 @@
         <v>86</v>
       </c>
       <c r="P216" t="n">
-        <v>11042</v>
+        <v>11041</v>
       </c>
       <c r="Q216" t="n">
         <v>1</v>
@@ -18614,7 +18617,7 @@
         <v>86</v>
       </c>
       <c r="P219" t="n">
-        <v>11066</v>
+        <v>11065</v>
       </c>
       <c r="Q219" t="n">
         <v>1</v>
@@ -18984,7 +18987,7 @@
         <v>86</v>
       </c>
       <c r="P224" t="n">
-        <v>10978</v>
+        <v>10976</v>
       </c>
       <c r="Q224" t="n">
         <v>1</v>
@@ -19354,7 +19357,7 @@
         <v>86</v>
       </c>
       <c r="P229" t="n">
-        <v>11068</v>
+        <v>11067</v>
       </c>
       <c r="Q229" t="n">
         <v>1</v>
@@ -19576,7 +19579,7 @@
         <v>86</v>
       </c>
       <c r="P232" t="n">
-        <v>11040</v>
+        <v>11041</v>
       </c>
       <c r="Q232" t="n">
         <v>1</v>
@@ -19650,7 +19653,7 @@
         <v>86</v>
       </c>
       <c r="P233" t="n">
-        <v>10936</v>
+        <v>10937</v>
       </c>
       <c r="Q233" t="n">
         <v>1</v>
@@ -19724,7 +19727,7 @@
         <v>86</v>
       </c>
       <c r="P234" t="n">
-        <v>11058</v>
+        <v>11059</v>
       </c>
       <c r="Q234" t="n">
         <v>1</v>
@@ -20760,7 +20763,7 @@
         <v>86</v>
       </c>
       <c r="P248" t="n">
-        <v>11067</v>
+        <v>11066</v>
       </c>
       <c r="Q248" t="n">
         <v>1</v>
@@ -21278,7 +21281,7 @@
         <v>86</v>
       </c>
       <c r="P255" t="n">
-        <v>10969</v>
+        <v>10968</v>
       </c>
       <c r="Q255" t="n">
         <v>1</v>
@@ -21500,7 +21503,7 @@
         <v>86</v>
       </c>
       <c r="P258" t="n">
-        <v>11060</v>
+        <v>11061</v>
       </c>
       <c r="Q258" t="n">
         <v>1</v>
@@ -21796,7 +21799,7 @@
         <v>86</v>
       </c>
       <c r="P262" t="n">
-        <v>11057</v>
+        <v>11058</v>
       </c>
       <c r="Q262" t="n">
         <v>1</v>
@@ -21944,7 +21947,7 @@
         <v>86</v>
       </c>
       <c r="P264" t="n">
-        <v>11062</v>
+        <v>11063</v>
       </c>
       <c r="Q264" t="n">
         <v>1</v>
@@ -22018,7 +22021,7 @@
         <v>86</v>
       </c>
       <c r="P265" t="n">
-        <v>11054</v>
+        <v>11053</v>
       </c>
       <c r="Q265" t="n">
         <v>1</v>
@@ -22462,7 +22465,7 @@
         <v>86</v>
       </c>
       <c r="P271" t="n">
-        <v>10988</v>
+        <v>10989</v>
       </c>
       <c r="Q271" t="n">
         <v>1</v>
@@ -22906,7 +22909,7 @@
         <v>86</v>
       </c>
       <c r="P277" t="n">
-        <v>10821</v>
+        <v>10822</v>
       </c>
       <c r="Q277" t="n">
         <v>1</v>
@@ -22980,7 +22983,7 @@
         <v>86</v>
       </c>
       <c r="P278" t="n">
-        <v>10851</v>
+        <v>10849</v>
       </c>
       <c r="Q278" t="n">
         <v>1</v>
@@ -23054,7 +23057,7 @@
         <v>86</v>
       </c>
       <c r="P279" t="n">
-        <v>10716</v>
+        <v>10720</v>
       </c>
       <c r="Q279" t="n">
         <v>1</v>
@@ -23202,7 +23205,7 @@
         <v>86</v>
       </c>
       <c r="P281" t="n">
-        <v>10853</v>
+        <v>10851</v>
       </c>
       <c r="Q281" t="n">
         <v>1</v>
@@ -23646,7 +23649,7 @@
         <v>86</v>
       </c>
       <c r="P287" t="n">
-        <v>11070</v>
+        <v>11069</v>
       </c>
       <c r="Q287" t="n">
         <v>1</v>
@@ -23720,7 +23723,7 @@
         <v>86</v>
       </c>
       <c r="P288" t="n">
-        <v>11063</v>
+        <v>11064</v>
       </c>
       <c r="Q288" t="n">
         <v>1</v>
@@ -23868,7 +23871,7 @@
         <v>86</v>
       </c>
       <c r="P290" t="n">
-        <v>11080</v>
+        <v>11081</v>
       </c>
       <c r="Q290" t="n">
         <v>1</v>
@@ -24016,7 +24019,7 @@
         <v>86</v>
       </c>
       <c r="P292" t="n">
-        <v>11057</v>
+        <v>11056</v>
       </c>
       <c r="Q292" t="n">
         <v>1</v>
@@ -24164,7 +24167,7 @@
         <v>86</v>
       </c>
       <c r="P294" t="n">
-        <v>11058</v>
+        <v>11057</v>
       </c>
       <c r="Q294" t="n">
         <v>1</v>
@@ -24238,7 +24241,7 @@
         <v>86</v>
       </c>
       <c r="P295" t="n">
-        <v>11004</v>
+        <v>11002</v>
       </c>
       <c r="Q295" t="n">
         <v>1</v>
@@ -24312,7 +24315,7 @@
         <v>86</v>
       </c>
       <c r="P296" t="n">
-        <v>11078</v>
+        <v>11079</v>
       </c>
       <c r="Q296" t="n">
         <v>1</v>
@@ -24682,7 +24685,7 @@
         <v>86</v>
       </c>
       <c r="P301" t="n">
-        <v>11080</v>
+        <v>11081</v>
       </c>
       <c r="Q301" t="n">
         <v>1</v>
@@ -24978,7 +24981,7 @@
         <v>86</v>
       </c>
       <c r="P305" t="n">
-        <v>11024</v>
+        <v>11023</v>
       </c>
       <c r="Q305" t="n">
         <v>1</v>
@@ -25126,7 +25129,7 @@
         <v>86</v>
       </c>
       <c r="P307" t="n">
-        <v>11077</v>
+        <v>11076</v>
       </c>
       <c r="Q307" t="n">
         <v>1</v>
@@ -25644,7 +25647,7 @@
         <v>86</v>
       </c>
       <c r="P314" t="n">
-        <v>11069</v>
+        <v>11070</v>
       </c>
       <c r="Q314" t="n">
         <v>1</v>
@@ -25866,7 +25869,7 @@
         <v>86</v>
       </c>
       <c r="P317" t="n">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="Q317" t="n">
         <v>1</v>
@@ -26076,7 +26079,7 @@
         <v>1</v>
       </c>
       <c r="L320" t="n">
-        <v>1.32231046262026e-275</v>
+        <v>4.74361169323443e-273</v>
       </c>
       <c r="M320" t="n">
         <v>1</v>
@@ -26088,7 +26091,7 @@
         <v>86</v>
       </c>
       <c r="P320" t="n">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="Q320" t="n">
         <v>1</v>
@@ -26162,7 +26165,7 @@
         <v>86</v>
       </c>
       <c r="P321" t="n">
-        <v>11075</v>
+        <v>11074</v>
       </c>
       <c r="Q321" t="n">
         <v>1</v>
@@ -26224,7 +26227,7 @@
         <v>1</v>
       </c>
       <c r="L322" t="n">
-        <v>2.39415423806856e-279</v>
+        <v>1.63513384906032e-271</v>
       </c>
       <c r="M322" t="n">
         <v>1</v>
@@ -26236,7 +26239,7 @@
         <v>86</v>
       </c>
       <c r="P322" t="n">
-        <v>10989</v>
+        <v>10991</v>
       </c>
       <c r="Q322" t="n">
         <v>1</v>
@@ -26298,7 +26301,7 @@
         <v>1</v>
       </c>
       <c r="L323" t="n">
-        <v>6.09147805058194e-297</v>
+        <v>2.82719142098489e-303</v>
       </c>
       <c r="M323" t="n">
         <v>1</v>
@@ -26310,7 +26313,7 @@
         <v>86</v>
       </c>
       <c r="P323" t="n">
-        <v>10968</v>
+        <v>10965</v>
       </c>
       <c r="Q323" t="n">
         <v>1</v>
@@ -26372,7 +26375,7 @@
         <v>1</v>
       </c>
       <c r="L324" t="n">
-        <v>2.08079510756545e-291</v>
+        <v>3.12944721124963e-293</v>
       </c>
       <c r="M324" t="n">
         <v>1</v>
@@ -26384,7 +26387,7 @@
         <v>86</v>
       </c>
       <c r="P324" t="n">
-        <v>10969</v>
+        <v>10970</v>
       </c>
       <c r="Q324" t="n">
         <v>1</v>
@@ -26458,7 +26461,7 @@
         <v>86</v>
       </c>
       <c r="P325" t="n">
-        <v>10979</v>
+        <v>10976</v>
       </c>
       <c r="Q325" t="n">
         <v>1</v>
@@ -26532,7 +26535,7 @@
         <v>86</v>
       </c>
       <c r="P326" t="n">
-        <v>10987</v>
+        <v>10988</v>
       </c>
       <c r="Q326" t="n">
         <v>1</v>
@@ -26594,7 +26597,7 @@
         <v>1</v>
       </c>
       <c r="L327" t="n">
-        <v>1.10200149804316e-207</v>
+        <v>1.76756878659679e-206</v>
       </c>
       <c r="M327" t="n">
         <v>1</v>
@@ -26606,7 +26609,7 @@
         <v>86</v>
       </c>
       <c r="P327" t="n">
-        <v>10875</v>
+        <v>10870</v>
       </c>
       <c r="Q327" t="n">
         <v>1</v>
@@ -26742,7 +26745,7 @@
         <v>1</v>
       </c>
       <c r="L329" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000151658478280222</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000108111225210847</v>
       </c>
       <c r="M329" t="n">
         <v>1</v>
@@ -26754,7 +26757,7 @@
         <v>86</v>
       </c>
       <c r="P329" t="n">
-        <v>10971</v>
+        <v>10972</v>
       </c>
       <c r="Q329" t="n">
         <v>1</v>
@@ -26828,7 +26831,7 @@
         <v>86</v>
       </c>
       <c r="P330" t="n">
-        <v>10983</v>
+        <v>10985</v>
       </c>
       <c r="Q330" t="n">
         <v>1</v>
@@ -26890,7 +26893,7 @@
         <v>1</v>
       </c>
       <c r="L331" t="n">
-        <v>5.95223516196737e-310</v>
+        <v>2.49512963425625e-303</v>
       </c>
       <c r="M331" t="n">
         <v>1</v>
@@ -26902,7 +26905,7 @@
         <v>86</v>
       </c>
       <c r="P331" t="n">
-        <v>10919</v>
+        <v>10918</v>
       </c>
       <c r="Q331" t="n">
         <v>1</v>
@@ -26976,7 +26979,7 @@
         <v>86</v>
       </c>
       <c r="P332" t="n">
-        <v>10795</v>
+        <v>10792</v>
       </c>
       <c r="Q332" t="n">
         <v>1</v>
@@ -27124,7 +27127,7 @@
         <v>86</v>
       </c>
       <c r="P334" t="n">
-        <v>10840</v>
+        <v>10838</v>
       </c>
       <c r="Q334" t="n">
         <v>1</v>
@@ -27198,7 +27201,7 @@
         <v>86</v>
       </c>
       <c r="P335" t="n">
-        <v>10923</v>
+        <v>10924</v>
       </c>
       <c r="Q335" t="n">
         <v>1</v>
@@ -27260,7 +27263,7 @@
         <v>1</v>
       </c>
       <c r="L336" t="n">
-        <v>3.87268896419502e-290</v>
+        <v>2.44392539901992e-287</v>
       </c>
       <c r="M336" t="n">
         <v>1</v>
@@ -27272,7 +27275,7 @@
         <v>86</v>
       </c>
       <c r="P336" t="n">
-        <v>10979</v>
+        <v>10981</v>
       </c>
       <c r="Q336" t="n">
         <v>1</v>
@@ -27420,7 +27423,7 @@
         <v>86</v>
       </c>
       <c r="P338" t="n">
-        <v>10919</v>
+        <v>10922</v>
       </c>
       <c r="Q338" t="n">
         <v>1</v>
@@ -27568,7 +27571,7 @@
         <v>86</v>
       </c>
       <c r="P340" t="n">
-        <v>10958</v>
+        <v>10957</v>
       </c>
       <c r="Q340" t="n">
         <v>1</v>
@@ -27716,7 +27719,7 @@
         <v>86</v>
       </c>
       <c r="P342" t="n">
-        <v>10922</v>
+        <v>10919</v>
       </c>
       <c r="Q342" t="n">
         <v>1</v>
@@ -27864,7 +27867,7 @@
         <v>86</v>
       </c>
       <c r="P344" t="n">
-        <v>10963</v>
+        <v>10960</v>
       </c>
       <c r="Q344" t="n">
         <v>1</v>
@@ -27938,7 +27941,7 @@
         <v>86</v>
       </c>
       <c r="P345" t="n">
-        <v>10939</v>
+        <v>10941</v>
       </c>
       <c r="Q345" t="n">
         <v>1</v>
@@ -28012,7 +28015,7 @@
         <v>86</v>
       </c>
       <c r="P346" t="n">
-        <v>10920</v>
+        <v>10921</v>
       </c>
       <c r="Q346" t="n">
         <v>1</v>
@@ -28086,7 +28089,7 @@
         <v>86</v>
       </c>
       <c r="P347" t="n">
-        <v>10927</v>
+        <v>10924</v>
       </c>
       <c r="Q347" t="n">
         <v>1</v>
@@ -28234,7 +28237,7 @@
         <v>86</v>
       </c>
       <c r="P349" t="n">
-        <v>10869</v>
+        <v>10870</v>
       </c>
       <c r="Q349" t="n">
         <v>1</v>
@@ -28308,7 +28311,7 @@
         <v>86</v>
       </c>
       <c r="P350" t="n">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="Q350" t="n">
         <v>1</v>
@@ -28382,7 +28385,7 @@
         <v>86</v>
       </c>
       <c r="P351" t="n">
-        <v>10932</v>
+        <v>10930</v>
       </c>
       <c r="Q351" t="n">
         <v>1</v>
@@ -28678,7 +28681,7 @@
         <v>86</v>
       </c>
       <c r="P355" t="n">
-        <v>10980</v>
+        <v>10979</v>
       </c>
       <c r="Q355" t="n">
         <v>1</v>
@@ -28752,7 +28755,7 @@
         <v>86</v>
       </c>
       <c r="P356" t="n">
-        <v>10967</v>
+        <v>10966</v>
       </c>
       <c r="Q356" t="n">
         <v>1</v>
@@ -28888,7 +28891,7 @@
         <v>1</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>1.46382688511946e-316</v>
       </c>
       <c r="M358" t="n">
         <v>1</v>
@@ -28900,7 +28903,7 @@
         <v>86</v>
       </c>
       <c r="P358" t="n">
-        <v>10981</v>
+        <v>10982</v>
       </c>
       <c r="Q358" t="n">
         <v>1</v>
@@ -28974,7 +28977,7 @@
         <v>86</v>
       </c>
       <c r="P359" t="n">
-        <v>10977</v>
+        <v>10978</v>
       </c>
       <c r="Q359" t="n">
         <v>1</v>
@@ -29048,7 +29051,7 @@
         <v>86</v>
       </c>
       <c r="P360" t="n">
-        <v>10983</v>
+        <v>10984</v>
       </c>
       <c r="Q360" t="n">
         <v>1</v>
@@ -29110,7 +29113,7 @@
         <v>1</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>9.33191191864946e-320</v>
       </c>
       <c r="M361" t="n">
         <v>1</v>
@@ -29122,7 +29125,7 @@
         <v>86</v>
       </c>
       <c r="P361" t="n">
-        <v>10980</v>
+        <v>10981</v>
       </c>
       <c r="Q361" t="n">
         <v>1</v>
@@ -29184,7 +29187,7 @@
         <v>1</v>
       </c>
       <c r="L362" t="n">
-        <v>2.4809051219573e-259</v>
+        <v>7.64422002215867e-260</v>
       </c>
       <c r="M362" t="n">
         <v>1</v>
@@ -29196,7 +29199,7 @@
         <v>86</v>
       </c>
       <c r="P362" t="n">
-        <v>10911</v>
+        <v>10909</v>
       </c>
       <c r="Q362" t="n">
         <v>1</v>
@@ -29258,7 +29261,7 @@
         <v>1</v>
       </c>
       <c r="L363" t="n">
-        <v>2.46602860403261e-262</v>
+        <v>2.87543273377568e-263</v>
       </c>
       <c r="M363" t="n">
         <v>1</v>
@@ -29270,7 +29273,7 @@
         <v>86</v>
       </c>
       <c r="P363" t="n">
-        <v>10886</v>
+        <v>10878</v>
       </c>
       <c r="Q363" t="n">
         <v>1</v>
@@ -29332,7 +29335,7 @@
         <v>1</v>
       </c>
       <c r="L364" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000947182298304678</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000367397793561695</v>
       </c>
       <c r="M364" t="n">
         <v>1</v>
@@ -29406,7 +29409,7 @@
         <v>1</v>
       </c>
       <c r="L365" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000018813635426769</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000202664515412006</v>
       </c>
       <c r="M365" t="n">
         <v>1</v>
@@ -29418,7 +29421,7 @@
         <v>86</v>
       </c>
       <c r="P365" t="n">
-        <v>10972</v>
+        <v>10973</v>
       </c>
       <c r="Q365" t="n">
         <v>1</v>
@@ -29480,7 +29483,7 @@
         <v>1</v>
       </c>
       <c r="L366" t="n">
-        <v>4.77887023010994e-251</v>
+        <v>3.13596120565561e-251</v>
       </c>
       <c r="M366" t="n">
         <v>1</v>
@@ -29492,7 +29495,7 @@
         <v>86</v>
       </c>
       <c r="P366" t="n">
-        <v>10844</v>
+        <v>10849</v>
       </c>
       <c r="Q366" t="n">
         <v>1</v>
@@ -29566,7 +29569,7 @@
         <v>86</v>
       </c>
       <c r="P367" t="n">
-        <v>10906</v>
+        <v>10904</v>
       </c>
       <c r="Q367" t="n">
         <v>1</v>
@@ -29640,7 +29643,7 @@
         <v>86</v>
       </c>
       <c r="P368" t="n">
-        <v>10928</v>
+        <v>10932</v>
       </c>
       <c r="Q368" t="n">
         <v>1</v>
@@ -29714,7 +29717,7 @@
         <v>86</v>
       </c>
       <c r="P369" t="n">
-        <v>10946</v>
+        <v>10945</v>
       </c>
       <c r="Q369" t="n">
         <v>1</v>
@@ -29788,7 +29791,7 @@
         <v>86</v>
       </c>
       <c r="P370" t="n">
-        <v>10978</v>
+        <v>10980</v>
       </c>
       <c r="Q370" t="n">
         <v>1</v>
@@ -29924,7 +29927,7 @@
         <v>1</v>
       </c>
       <c r="L372" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000026928891625607</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000794118960048298</v>
       </c>
       <c r="M372" t="n">
         <v>1</v>
@@ -29998,7 +30001,7 @@
         <v>1</v>
       </c>
       <c r="L373" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000015529995075148</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000481259218177809</v>
       </c>
       <c r="M373" t="n">
         <v>1</v>
@@ -30010,7 +30013,7 @@
         <v>86</v>
       </c>
       <c r="P373" t="n">
-        <v>10971</v>
+        <v>10970</v>
       </c>
       <c r="Q373" t="n">
         <v>1</v>
@@ -30072,7 +30075,7 @@
         <v>1</v>
       </c>
       <c r="L374" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000433580307377059</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000354610139970413</v>
       </c>
       <c r="M374" t="n">
         <v>1</v>
@@ -30084,7 +30087,7 @@
         <v>86</v>
       </c>
       <c r="P374" t="n">
-        <v>10965</v>
+        <v>10967</v>
       </c>
       <c r="Q374" t="n">
         <v>1</v>
@@ -30146,7 +30149,7 @@
         <v>1</v>
       </c>
       <c r="L375" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000034320832788923</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000674260336832089</v>
       </c>
       <c r="M375" t="n">
         <v>1</v>
@@ -30158,7 +30161,7 @@
         <v>86</v>
       </c>
       <c r="P375" t="n">
-        <v>10973</v>
+        <v>10971</v>
       </c>
       <c r="Q375" t="n">
         <v>1</v>
@@ -30220,7 +30223,7 @@
         <v>1</v>
       </c>
       <c r="L376" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000272238855861383</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000602100064819523</v>
       </c>
       <c r="M376" t="n">
         <v>1</v>
@@ -30232,7 +30235,7 @@
         <v>86</v>
       </c>
       <c r="P376" t="n">
-        <v>10960</v>
+        <v>10961</v>
       </c>
       <c r="Q376" t="n">
         <v>0.833333333333333</v>
@@ -30276,10 +30279,10 @@
         <v>412</v>
       </c>
       <c r="F377" t="s">
-        <v>85</v>
+        <v>403</v>
       </c>
       <c r="G377" t="s">
-        <v>86</v>
+        <v>413</v>
       </c>
       <c r="H377" t="b">
         <v>0</v>
@@ -30291,19 +30294,19 @@
         <v>11000</v>
       </c>
       <c r="K377" t="n">
-        <v>0.988317895570792</v>
+        <v>0.5281637130083</v>
       </c>
       <c r="L377" t="n">
-        <v>0.0116821044292078</v>
+        <v>0.4718362869917</v>
       </c>
       <c r="M377" t="n">
-        <v>0.976635791141584</v>
+        <v>0.0563274260165994</v>
       </c>
       <c r="N377" t="s">
-        <v>85</v>
+        <v>414</v>
       </c>
       <c r="O377" t="s">
-        <v>86</v>
+        <v>415</v>
       </c>
       <c r="P377" t="n">
         <v>10801</v>
@@ -30368,7 +30371,7 @@
         <v>1</v>
       </c>
       <c r="L378" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000857365263493119</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000691695758491187</v>
       </c>
       <c r="M378" t="n">
         <v>1</v>
@@ -30380,7 +30383,7 @@
         <v>86</v>
       </c>
       <c r="P378" t="n">
-        <v>10988</v>
+        <v>10987</v>
       </c>
       <c r="Q378" t="n">
         <v>1</v>
@@ -30442,7 +30445,7 @@
         <v>1</v>
       </c>
       <c r="L379" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000113849784214419</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000023054754339792</v>
       </c>
       <c r="M379" t="n">
         <v>1</v>
@@ -30516,7 +30519,7 @@
         <v>1</v>
       </c>
       <c r="L380" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000255151189961766</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000139753879598003</v>
       </c>
       <c r="M380" t="n">
         <v>1</v>
@@ -30590,7 +30593,7 @@
         <v>1</v>
       </c>
       <c r="L381" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000885752047321463</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000347978720612159</v>
       </c>
       <c r="M381" t="n">
         <v>1</v>
@@ -30664,7 +30667,7 @@
         <v>1</v>
       </c>
       <c r="L382" t="n">
-        <v>8.01108343169875e-217</v>
+        <v>2.25108608177752e-213</v>
       </c>
       <c r="M382" t="n">
         <v>1</v>
@@ -30720,10 +30723,10 @@
         <v>412</v>
       </c>
       <c r="F383" t="s">
-        <v>85</v>
+        <v>403</v>
       </c>
       <c r="G383" t="s">
-        <v>86</v>
+        <v>410</v>
       </c>
       <c r="H383" t="b">
         <v>1</v>
@@ -30738,7 +30741,7 @@
         <v>1</v>
       </c>
       <c r="L383" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000516910720183825</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000114854925993132</v>
       </c>
       <c r="M383" t="n">
         <v>1</v>
@@ -30750,10 +30753,10 @@
         <v>86</v>
       </c>
       <c r="P383" t="n">
-        <v>10964</v>
+        <v>10962</v>
       </c>
       <c r="Q383" t="n">
-        <v>1</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="R383" t="n">
         <v>1</v>
@@ -30762,7 +30765,7 @@
         <v>0.5</v>
       </c>
       <c r="T383" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="U383" t="n">
         <v>16</v>
@@ -30812,7 +30815,7 @@
         <v>1</v>
       </c>
       <c r="L384" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000261656337509835</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000879679490374572</v>
       </c>
       <c r="M384" t="n">
         <v>1</v>
@@ -30824,7 +30827,7 @@
         <v>86</v>
       </c>
       <c r="P384" t="n">
-        <v>10834</v>
+        <v>10838</v>
       </c>
       <c r="Q384" t="n">
         <v>1</v>
@@ -30886,7 +30889,7 @@
         <v>1</v>
       </c>
       <c r="L385" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000820561878145265</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407464073440245</v>
       </c>
       <c r="M385" t="n">
         <v>1</v>
@@ -30898,7 +30901,7 @@
         <v>86</v>
       </c>
       <c r="P385" t="n">
-        <v>10942</v>
+        <v>10946</v>
       </c>
       <c r="Q385" t="n">
         <v>1</v>
@@ -30960,7 +30963,7 @@
         <v>1</v>
       </c>
       <c r="L386" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000163152298242491</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000113398289078354</v>
       </c>
       <c r="M386" t="n">
         <v>1</v>
@@ -30972,7 +30975,7 @@
         <v>86</v>
       </c>
       <c r="P386" t="n">
-        <v>10739</v>
+        <v>10744</v>
       </c>
       <c r="Q386" t="n">
         <v>1</v>
@@ -31034,7 +31037,7 @@
         <v>1</v>
       </c>
       <c r="L387" t="n">
-        <v>3.58523296948447e-244</v>
+        <v>5.59776329637651e-242</v>
       </c>
       <c r="M387" t="n">
         <v>1</v>
@@ -31046,7 +31049,7 @@
         <v>86</v>
       </c>
       <c r="P387" t="n">
-        <v>10988</v>
+        <v>10987</v>
       </c>
       <c r="Q387" t="n">
         <v>1</v>
@@ -31108,7 +31111,7 @@
         <v>1</v>
       </c>
       <c r="L388" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000577300164308386</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000116725017617262</v>
       </c>
       <c r="M388" t="n">
         <v>1</v>
@@ -31182,7 +31185,7 @@
         <v>1</v>
       </c>
       <c r="L389" t="n">
-        <v>6.20590721506627e-229</v>
+        <v>9.63177277869518e-227</v>
       </c>
       <c r="M389" t="n">
         <v>1</v>
@@ -31194,7 +31197,7 @@
         <v>86</v>
       </c>
       <c r="P389" t="n">
-        <v>10991</v>
+        <v>10992</v>
       </c>
       <c r="Q389" t="n">
         <v>1</v>
@@ -31256,7 +31259,7 @@
         <v>1</v>
       </c>
       <c r="L390" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000928720059720345</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000151879538640091</v>
       </c>
       <c r="M390" t="n">
         <v>1</v>
@@ -31330,7 +31333,7 @@
         <v>1</v>
       </c>
       <c r="L391" t="n">
-        <v>1.29348426704653e-206</v>
+        <v>2.3164982966873e-211</v>
       </c>
       <c r="M391" t="n">
         <v>1</v>
@@ -31342,7 +31345,7 @@
         <v>86</v>
       </c>
       <c r="P391" t="n">
-        <v>10964</v>
+        <v>10962</v>
       </c>
       <c r="Q391" t="n">
         <v>1</v>
@@ -31416,7 +31419,7 @@
         <v>86</v>
       </c>
       <c r="P392" t="n">
-        <v>10982</v>
+        <v>10981</v>
       </c>
       <c r="Q392" t="n">
         <v>1</v>
@@ -31490,7 +31493,7 @@
         <v>86</v>
       </c>
       <c r="P393" t="n">
-        <v>10983</v>
+        <v>10982</v>
       </c>
       <c r="Q393" t="n">
         <v>1</v>
@@ -31552,7 +31555,7 @@
         <v>1</v>
       </c>
       <c r="L394" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000201593456842161</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000486260653503096</v>
       </c>
       <c r="M394" t="n">
         <v>1</v>
@@ -31626,7 +31629,7 @@
         <v>1</v>
       </c>
       <c r="L395" t="n">
-        <v>7.53415571626585e-264</v>
+        <v>3.93907491480297e-254</v>
       </c>
       <c r="M395" t="n">
         <v>1</v>
@@ -31700,7 +31703,7 @@
         <v>1</v>
       </c>
       <c r="L396" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000328405430073168</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000284771408610299</v>
       </c>
       <c r="M396" t="n">
         <v>1</v>
@@ -31774,7 +31777,7 @@
         <v>1</v>
       </c>
       <c r="L397" t="n">
-        <v>2.35086018813474e-232</v>
+        <v>2.25739275409994e-222</v>
       </c>
       <c r="M397" t="n">
         <v>1</v>
@@ -31786,7 +31789,7 @@
         <v>86</v>
       </c>
       <c r="P397" t="n">
-        <v>10978</v>
+        <v>10976</v>
       </c>
       <c r="Q397" t="n">
         <v>1</v>
@@ -31848,7 +31851,7 @@
         <v>1</v>
       </c>
       <c r="L398" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000239375344361815</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000012706430383934</v>
       </c>
       <c r="M398" t="n">
         <v>1</v>
@@ -31860,7 +31863,7 @@
         <v>86</v>
       </c>
       <c r="P398" t="n">
-        <v>10914</v>
+        <v>10915</v>
       </c>
       <c r="Q398" t="n">
         <v>1</v>
@@ -31898,10 +31901,10 @@
         <v>279</v>
       </c>
       <c r="D399" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E399" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F399" t="s">
         <v>85</v>
@@ -31913,7 +31916,7 @@
         <v>1</v>
       </c>
       <c r="I399" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J399" t="n">
         <v>11000</v>
@@ -31922,7 +31925,7 @@
         <v>1</v>
       </c>
       <c r="L399" t="n">
-        <v>1.0529028162729e-288</v>
+        <v>6.40459374525058e-284</v>
       </c>
       <c r="M399" t="n">
         <v>1</v>
@@ -31934,7 +31937,7 @@
         <v>86</v>
       </c>
       <c r="P399" t="n">
-        <v>10928</v>
+        <v>10925</v>
       </c>
       <c r="Q399" t="n">
         <v>1</v>
@@ -31972,10 +31975,10 @@
         <v>280</v>
       </c>
       <c r="D400" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E400" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F400" t="s">
         <v>85</v>
@@ -31987,7 +31990,7 @@
         <v>1</v>
       </c>
       <c r="I400" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J400" t="n">
         <v>11000</v>
@@ -31996,7 +31999,7 @@
         <v>1</v>
       </c>
       <c r="L400" t="n">
-        <v>7.01209323056656e-283</v>
+        <v>1.78672934440343e-268</v>
       </c>
       <c r="M400" t="n">
         <v>1</v>
@@ -32046,10 +32049,10 @@
         <v>281</v>
       </c>
       <c r="D401" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E401" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F401" t="s">
         <v>85</v>
@@ -32061,7 +32064,7 @@
         <v>1</v>
       </c>
       <c r="I401" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J401" t="n">
         <v>11000</v>
@@ -32070,7 +32073,7 @@
         <v>1</v>
       </c>
       <c r="L401" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000106420412205866</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000839428536425685</v>
       </c>
       <c r="M401" t="n">
         <v>1</v>
@@ -32082,7 +32085,7 @@
         <v>86</v>
       </c>
       <c r="P401" t="n">
-        <v>10950</v>
+        <v>10947</v>
       </c>
       <c r="Q401" t="n">
         <v>1</v>
@@ -32120,10 +32123,10 @@
         <v>282</v>
       </c>
       <c r="D402" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E402" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F402" t="s">
         <v>85</v>
@@ -32135,7 +32138,7 @@
         <v>1</v>
       </c>
       <c r="I402" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J402" t="n">
         <v>11000</v>
@@ -32144,7 +32147,7 @@
         <v>1</v>
       </c>
       <c r="L402" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000799040370387031</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000113109889158583</v>
       </c>
       <c r="M402" t="n">
         <v>1</v>
@@ -32194,10 +32197,10 @@
         <v>283</v>
       </c>
       <c r="D403" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E403" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F403" t="s">
         <v>85</v>
@@ -32209,7 +32212,7 @@
         <v>1</v>
       </c>
       <c r="I403" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J403" t="n">
         <v>11000</v>
@@ -32218,7 +32221,7 @@
         <v>1</v>
       </c>
       <c r="L403" t="n">
-        <v>2.77173868189308e-213</v>
+        <v>1.31879785343446e-219</v>
       </c>
       <c r="M403" t="n">
         <v>1</v>
@@ -32230,7 +32233,7 @@
         <v>86</v>
       </c>
       <c r="P403" t="n">
-        <v>10952</v>
+        <v>10954</v>
       </c>
       <c r="Q403" t="n">
         <v>1</v>
@@ -32292,7 +32295,7 @@
         <v>1</v>
       </c>
       <c r="L404" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000107277242590925</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000678222067756377</v>
       </c>
       <c r="M404" t="n">
         <v>1</v>
@@ -32304,7 +32307,7 @@
         <v>86</v>
       </c>
       <c r="P404" t="n">
-        <v>10938</v>
+        <v>10939</v>
       </c>
       <c r="Q404" t="n">
         <v>1</v>
@@ -32366,7 +32369,7 @@
         <v>1</v>
       </c>
       <c r="L405" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000012339197944912</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000258202651634633</v>
       </c>
       <c r="M405" t="n">
         <v>1</v>
@@ -32378,7 +32381,7 @@
         <v>86</v>
       </c>
       <c r="P405" t="n">
-        <v>7612</v>
+        <v>7645</v>
       </c>
       <c r="Q405" t="n">
         <v>0.833333333333333</v>
@@ -32440,7 +32443,7 @@
         <v>1</v>
       </c>
       <c r="L406" t="n">
-        <v>5.30336573449289e-269</v>
+        <v>4.20030800577577e-268</v>
       </c>
       <c r="M406" t="n">
         <v>1</v>
@@ -32514,7 +32517,7 @@
         <v>1</v>
       </c>
       <c r="L407" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294337381735508</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000143586920930281</v>
       </c>
       <c r="M407" t="n">
         <v>1</v>
@@ -32526,7 +32529,7 @@
         <v>86</v>
       </c>
       <c r="P407" t="n">
-        <v>10957</v>
+        <v>10959</v>
       </c>
       <c r="Q407" t="n">
         <v>1</v>
@@ -32588,7 +32591,7 @@
         <v>1</v>
       </c>
       <c r="L408" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000268855173805137</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000195171031599261</v>
       </c>
       <c r="M408" t="n">
         <v>1</v>
@@ -32600,7 +32603,7 @@
         <v>86</v>
       </c>
       <c r="P408" t="n">
-        <v>10876</v>
+        <v>10870</v>
       </c>
       <c r="Q408" t="n">
         <v>0.5</v>
@@ -32662,7 +32665,7 @@
         <v>1</v>
       </c>
       <c r="L409" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000423014897182277</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000462364726169445</v>
       </c>
       <c r="M409" t="n">
         <v>1</v>
@@ -32674,7 +32677,7 @@
         <v>86</v>
       </c>
       <c r="P409" t="n">
-        <v>10982</v>
+        <v>10981</v>
       </c>
       <c r="Q409" t="n">
         <v>1</v>
@@ -32736,7 +32739,7 @@
         <v>1</v>
       </c>
       <c r="L410" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000697722384032394</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000365770225910461</v>
       </c>
       <c r="M410" t="n">
         <v>1</v>
@@ -32789,7 +32792,7 @@
         <v>409</v>
       </c>
       <c r="E411" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F411" t="s">
         <v>403</v>
@@ -32798,22 +32801,22 @@
         <v>410</v>
       </c>
       <c r="H411" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I411" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J411" t="n">
         <v>11000</v>
       </c>
       <c r="K411" t="n">
-        <v>0.999999775818246</v>
+        <v>0.999190155193985</v>
       </c>
       <c r="L411" t="n">
-        <v>0.000000224181754137014</v>
+        <v>0.000809844806014791</v>
       </c>
       <c r="M411" t="n">
-        <v>0.999999551636492</v>
+        <v>0.99838031038797</v>
       </c>
       <c r="N411" t="s">
         <v>85</v>
@@ -32822,19 +32825,19 @@
         <v>86</v>
       </c>
       <c r="P411" t="n">
-        <v>10842</v>
+        <v>10850</v>
       </c>
       <c r="Q411" t="n">
-        <v>0.833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R411" t="n">
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="S411" t="n">
         <v>0.5</v>
       </c>
       <c r="T411" t="n">
-        <v>11000</v>
+        <v>5000</v>
       </c>
       <c r="U411" t="n">
         <v>16</v>
@@ -32884,7 +32887,7 @@
         <v>1</v>
       </c>
       <c r="L412" t="n">
-        <v>2.59717929081945e-212</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000497162164729199</v>
       </c>
       <c r="M412" t="n">
         <v>1</v>
@@ -32896,7 +32899,7 @@
         <v>86</v>
       </c>
       <c r="P412" t="n">
-        <v>10932</v>
+        <v>10930</v>
       </c>
       <c r="Q412" t="n">
         <v>1</v>
@@ -32958,7 +32961,7 @@
         <v>1</v>
       </c>
       <c r="L413" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000863643379412664</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000462162843868681</v>
       </c>
       <c r="M413" t="n">
         <v>1</v>
@@ -32970,7 +32973,7 @@
         <v>86</v>
       </c>
       <c r="P413" t="n">
-        <v>10964</v>
+        <v>10966</v>
       </c>
       <c r="Q413" t="n">
         <v>1</v>
@@ -33032,7 +33035,7 @@
         <v>1</v>
       </c>
       <c r="L414" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000368601361642564</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000105313272951112</v>
       </c>
       <c r="M414" t="n">
         <v>1</v>
@@ -33044,7 +33047,7 @@
         <v>86</v>
       </c>
       <c r="P414" t="n">
-        <v>10979</v>
+        <v>10981</v>
       </c>
       <c r="Q414" t="n">
         <v>1</v>
@@ -33106,7 +33109,7 @@
         <v>1</v>
       </c>
       <c r="L415" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000247573881524998</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000109915501538447</v>
       </c>
       <c r="M415" t="n">
         <v>1</v>
@@ -33180,7 +33183,7 @@
         <v>1</v>
       </c>
       <c r="L416" t="n">
-        <v>6.73287888976118e-289</v>
+        <v>3.0714382618497e-278</v>
       </c>
       <c r="M416" t="n">
         <v>1</v>
@@ -33192,7 +33195,7 @@
         <v>86</v>
       </c>
       <c r="P416" t="n">
-        <v>10923</v>
+        <v>10921</v>
       </c>
       <c r="Q416" t="n">
         <v>1</v>
@@ -33251,13 +33254,13 @@
         <v>11000</v>
       </c>
       <c r="K417" t="n">
-        <v>0.999998557813455</v>
+        <v>0.999999999703407</v>
       </c>
       <c r="L417" t="n">
-        <v>0.00000144218654450717</v>
+        <v>0.000000000296593464140821</v>
       </c>
       <c r="M417" t="n">
-        <v>0.999997115626911</v>
+        <v>0.999999999406813</v>
       </c>
       <c r="N417" t="s">
         <v>85</v>
@@ -33266,7 +33269,7 @@
         <v>86</v>
       </c>
       <c r="P417" t="n">
-        <v>10971</v>
+        <v>10973</v>
       </c>
       <c r="Q417" t="n">
         <v>1</v>
@@ -33328,7 +33331,7 @@
         <v>1</v>
       </c>
       <c r="L418" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256260333837239</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000357883462793815</v>
       </c>
       <c r="M418" t="n">
         <v>1</v>
@@ -33402,7 +33405,7 @@
         <v>1</v>
       </c>
       <c r="L419" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000077914966011338</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000292192334504558</v>
       </c>
       <c r="M419" t="n">
         <v>1</v>
@@ -33476,7 +33479,7 @@
         <v>1</v>
       </c>
       <c r="L420" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000205744262550913</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000437833157831268</v>
       </c>
       <c r="M420" t="n">
         <v>1</v>
@@ -33488,7 +33491,7 @@
         <v>86</v>
       </c>
       <c r="P420" t="n">
-        <v>10978</v>
+        <v>10977</v>
       </c>
       <c r="Q420" t="n">
         <v>1</v>
@@ -33550,7 +33553,7 @@
         <v>1</v>
       </c>
       <c r="L421" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000139246028999941</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000428756652588233</v>
       </c>
       <c r="M421" t="n">
         <v>1</v>
@@ -33562,7 +33565,7 @@
         <v>86</v>
       </c>
       <c r="P421" t="n">
-        <v>10980</v>
+        <v>10979</v>
       </c>
       <c r="Q421" t="n">
         <v>0.333333333333333</v>
@@ -33600,10 +33603,10 @@
         <v>367</v>
       </c>
       <c r="D422" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E422" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F422" t="s">
         <v>85</v>
@@ -33615,7 +33618,7 @@
         <v>1</v>
       </c>
       <c r="I422" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J422" t="n">
         <v>11000</v>
@@ -33624,7 +33627,7 @@
         <v>1</v>
       </c>
       <c r="L422" t="n">
-        <v>1.46054090893617e-277</v>
+        <v>1.96629281245918e-273</v>
       </c>
       <c r="M422" t="n">
         <v>1</v>
@@ -33636,7 +33639,7 @@
         <v>86</v>
       </c>
       <c r="P422" t="n">
-        <v>10918</v>
+        <v>10916</v>
       </c>
       <c r="Q422" t="n">
         <v>1</v>
@@ -33674,10 +33677,10 @@
         <v>368</v>
       </c>
       <c r="D423" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E423" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F423" t="s">
         <v>85</v>
@@ -33689,7 +33692,7 @@
         <v>1</v>
       </c>
       <c r="I423" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J423" t="n">
         <v>11000</v>
@@ -33698,7 +33701,7 @@
         <v>1</v>
       </c>
       <c r="L423" t="n">
-        <v>2.12228222442897e-233</v>
+        <v>2.16404499250166e-231</v>
       </c>
       <c r="M423" t="n">
         <v>1</v>
@@ -33710,7 +33713,7 @@
         <v>86</v>
       </c>
       <c r="P423" t="n">
-        <v>10831</v>
+        <v>10825</v>
       </c>
       <c r="Q423" t="n">
         <v>1</v>
@@ -33748,10 +33751,10 @@
         <v>369</v>
       </c>
       <c r="D424" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E424" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F424" t="s">
         <v>85</v>
@@ -33763,7 +33766,7 @@
         <v>1</v>
       </c>
       <c r="I424" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J424" t="n">
         <v>11000</v>
@@ -33772,7 +33775,7 @@
         <v>1</v>
       </c>
       <c r="L424" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000201562327720225</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000962190056942684</v>
       </c>
       <c r="M424" t="n">
         <v>1</v>
@@ -33784,7 +33787,7 @@
         <v>86</v>
       </c>
       <c r="P424" t="n">
-        <v>10868</v>
+        <v>10869</v>
       </c>
       <c r="Q424" t="n">
         <v>1</v>
@@ -33822,10 +33825,10 @@
         <v>370</v>
       </c>
       <c r="D425" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E425" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F425" t="s">
         <v>85</v>
@@ -33837,7 +33840,7 @@
         <v>1</v>
       </c>
       <c r="I425" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J425" t="n">
         <v>11000</v>
@@ -33846,7 +33849,7 @@
         <v>1</v>
       </c>
       <c r="L425" t="n">
-        <v>9.48038991297235e-207</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000127078577922681</v>
       </c>
       <c r="M425" t="n">
         <v>1</v>
@@ -33858,7 +33861,7 @@
         <v>86</v>
       </c>
       <c r="P425" t="n">
-        <v>10977</v>
+        <v>10975</v>
       </c>
       <c r="Q425" t="n">
         <v>1</v>
@@ -33896,10 +33899,10 @@
         <v>371</v>
       </c>
       <c r="D426" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E426" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F426" t="s">
         <v>85</v>
@@ -33911,7 +33914,7 @@
         <v>1</v>
       </c>
       <c r="I426" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J426" t="n">
         <v>11000</v>
@@ -33920,7 +33923,7 @@
         <v>1</v>
       </c>
       <c r="L426" t="n">
-        <v>9.39551705215257e-217</v>
+        <v>5.47624027521352e-214</v>
       </c>
       <c r="M426" t="n">
         <v>1</v>
@@ -33932,7 +33935,7 @@
         <v>86</v>
       </c>
       <c r="P426" t="n">
-        <v>10976</v>
+        <v>10974</v>
       </c>
       <c r="Q426" t="n">
         <v>1</v>
@@ -33970,10 +33973,10 @@
         <v>116</v>
       </c>
       <c r="D427" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E427" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F427" t="s">
         <v>85</v>
@@ -33985,7 +33988,7 @@
         <v>1</v>
       </c>
       <c r="I427" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J427" t="n">
         <v>11086</v>
@@ -34006,7 +34009,7 @@
         <v>86</v>
       </c>
       <c r="P427" t="n">
-        <v>11069</v>
+        <v>11068</v>
       </c>
       <c r="Q427" t="n">
         <v>1</v>
@@ -34044,10 +34047,10 @@
         <v>118</v>
       </c>
       <c r="D428" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E428" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F428" t="s">
         <v>85</v>
@@ -34059,7 +34062,7 @@
         <v>1</v>
       </c>
       <c r="I428" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J428" t="n">
         <v>11086</v>
@@ -34080,7 +34083,7 @@
         <v>86</v>
       </c>
       <c r="P428" t="n">
-        <v>11071</v>
+        <v>11070</v>
       </c>
       <c r="Q428" t="n">
         <v>1</v>
@@ -34118,10 +34121,10 @@
         <v>119</v>
       </c>
       <c r="D429" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E429" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F429" t="s">
         <v>85</v>
@@ -34133,7 +34136,7 @@
         <v>1</v>
       </c>
       <c r="I429" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J429" t="n">
         <v>11086</v>
@@ -34154,7 +34157,7 @@
         <v>86</v>
       </c>
       <c r="P429" t="n">
-        <v>11073</v>
+        <v>11074</v>
       </c>
       <c r="Q429" t="n">
         <v>1</v>
@@ -34192,10 +34195,10 @@
         <v>120</v>
       </c>
       <c r="D430" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E430" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F430" t="s">
         <v>85</v>
@@ -34207,7 +34210,7 @@
         <v>1</v>
       </c>
       <c r="I430" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J430" t="n">
         <v>11086</v>
@@ -34228,7 +34231,7 @@
         <v>86</v>
       </c>
       <c r="P430" t="n">
-        <v>11062</v>
+        <v>11061</v>
       </c>
       <c r="Q430" t="n">
         <v>1</v>
@@ -34266,10 +34269,10 @@
         <v>121</v>
       </c>
       <c r="D431" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E431" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F431" t="s">
         <v>85</v>
@@ -34281,7 +34284,7 @@
         <v>1</v>
       </c>
       <c r="I431" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J431" t="n">
         <v>11086</v>
@@ -34302,7 +34305,7 @@
         <v>86</v>
       </c>
       <c r="P431" t="n">
-        <v>11043</v>
+        <v>11042</v>
       </c>
       <c r="Q431" t="n">
         <v>1</v>
@@ -34340,10 +34343,10 @@
         <v>132</v>
       </c>
       <c r="D432" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E432" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F432" t="s">
         <v>85</v>
@@ -34355,7 +34358,7 @@
         <v>1</v>
       </c>
       <c r="I432" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J432" t="n">
         <v>11086</v>
@@ -34414,10 +34417,10 @@
         <v>133</v>
       </c>
       <c r="D433" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E433" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F433" t="s">
         <v>85</v>
@@ -34429,7 +34432,7 @@
         <v>1</v>
       </c>
       <c r="I433" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J433" t="n">
         <v>11086</v>
@@ -34450,7 +34453,7 @@
         <v>86</v>
       </c>
       <c r="P433" t="n">
-        <v>11018</v>
+        <v>11016</v>
       </c>
       <c r="Q433" t="n">
         <v>1</v>
@@ -34488,10 +34491,10 @@
         <v>134</v>
       </c>
       <c r="D434" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E434" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F434" t="s">
         <v>85</v>
@@ -34503,7 +34506,7 @@
         <v>1</v>
       </c>
       <c r="I434" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J434" t="n">
         <v>11086</v>
@@ -34562,10 +34565,10 @@
         <v>135</v>
       </c>
       <c r="D435" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E435" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F435" t="s">
         <v>85</v>
@@ -34577,7 +34580,7 @@
         <v>1</v>
       </c>
       <c r="I435" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J435" t="n">
         <v>11086</v>
@@ -34636,10 +34639,10 @@
         <v>136</v>
       </c>
       <c r="D436" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E436" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F436" t="s">
         <v>85</v>
@@ -34651,7 +34654,7 @@
         <v>1</v>
       </c>
       <c r="I436" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J436" t="n">
         <v>11086</v>
@@ -34710,10 +34713,10 @@
         <v>137</v>
       </c>
       <c r="D437" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E437" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F437" t="s">
         <v>85</v>
@@ -34725,7 +34728,7 @@
         <v>1</v>
       </c>
       <c r="I437" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J437" t="n">
         <v>11086</v>
@@ -34746,7 +34749,7 @@
         <v>86</v>
       </c>
       <c r="P437" t="n">
-        <v>11054</v>
+        <v>11052</v>
       </c>
       <c r="Q437" t="n">
         <v>1</v>
@@ -34784,10 +34787,10 @@
         <v>138</v>
       </c>
       <c r="D438" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E438" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F438" t="s">
         <v>85</v>
@@ -34799,7 +34802,7 @@
         <v>1</v>
       </c>
       <c r="I438" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J438" t="n">
         <v>11086</v>
@@ -34820,7 +34823,7 @@
         <v>86</v>
       </c>
       <c r="P438" t="n">
-        <v>11057</v>
+        <v>11056</v>
       </c>
       <c r="Q438" t="n">
         <v>1</v>
@@ -34858,10 +34861,10 @@
         <v>139</v>
       </c>
       <c r="D439" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E439" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F439" t="s">
         <v>85</v>
@@ -34873,7 +34876,7 @@
         <v>1</v>
       </c>
       <c r="I439" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J439" t="n">
         <v>11086</v>
@@ -34932,10 +34935,10 @@
         <v>140</v>
       </c>
       <c r="D440" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E440" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F440" t="s">
         <v>85</v>
@@ -34947,7 +34950,7 @@
         <v>1</v>
       </c>
       <c r="I440" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J440" t="n">
         <v>11086</v>
@@ -34968,7 +34971,7 @@
         <v>86</v>
       </c>
       <c r="P440" t="n">
-        <v>11055</v>
+        <v>11057</v>
       </c>
       <c r="Q440" t="n">
         <v>1</v>
@@ -35006,10 +35009,10 @@
         <v>141</v>
       </c>
       <c r="D441" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E441" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F441" t="s">
         <v>85</v>
@@ -35021,7 +35024,7 @@
         <v>1</v>
       </c>
       <c r="I441" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J441" t="n">
         <v>11086</v>
@@ -35042,7 +35045,7 @@
         <v>86</v>
       </c>
       <c r="P441" t="n">
-        <v>10202</v>
+        <v>10200</v>
       </c>
       <c r="Q441" t="n">
         <v>1</v>
@@ -35080,10 +35083,10 @@
         <v>142</v>
       </c>
       <c r="D442" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E442" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F442" t="s">
         <v>85</v>
@@ -35095,7 +35098,7 @@
         <v>1</v>
       </c>
       <c r="I442" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J442" t="n">
         <v>11086</v>
@@ -35104,7 +35107,7 @@
         <v>1</v>
       </c>
       <c r="L442" t="n">
-        <v>2.38297597302253e-239</v>
+        <v>1.4730219087491e-241</v>
       </c>
       <c r="M442" t="n">
         <v>1</v>
@@ -35116,7 +35119,7 @@
         <v>86</v>
       </c>
       <c r="P442" t="n">
-        <v>11070</v>
+        <v>11069</v>
       </c>
       <c r="Q442" t="n">
         <v>1</v>
@@ -35154,10 +35157,10 @@
         <v>143</v>
       </c>
       <c r="D443" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E443" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F443" t="s">
         <v>85</v>
@@ -35169,7 +35172,7 @@
         <v>1</v>
       </c>
       <c r="I443" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J443" t="n">
         <v>11086</v>
@@ -35190,7 +35193,7 @@
         <v>86</v>
       </c>
       <c r="P443" t="n">
-        <v>11049</v>
+        <v>11046</v>
       </c>
       <c r="Q443" t="n">
         <v>1</v>
@@ -35228,10 +35231,10 @@
         <v>144</v>
       </c>
       <c r="D444" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E444" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F444" t="s">
         <v>85</v>
@@ -35243,7 +35246,7 @@
         <v>1</v>
       </c>
       <c r="I444" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J444" t="n">
         <v>11086</v>
@@ -35302,10 +35305,10 @@
         <v>145</v>
       </c>
       <c r="D445" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E445" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F445" t="s">
         <v>85</v>
@@ -35317,7 +35320,7 @@
         <v>1</v>
       </c>
       <c r="I445" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J445" t="n">
         <v>11086</v>
@@ -35326,7 +35329,7 @@
         <v>1</v>
       </c>
       <c r="L445" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000109453681529661</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000116517655499039</v>
       </c>
       <c r="M445" t="n">
         <v>1</v>
@@ -35338,7 +35341,7 @@
         <v>86</v>
       </c>
       <c r="P445" t="n">
-        <v>11072</v>
+        <v>11071</v>
       </c>
       <c r="Q445" t="n">
         <v>1</v>
@@ -35376,10 +35379,10 @@
         <v>146</v>
       </c>
       <c r="D446" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E446" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F446" t="s">
         <v>85</v>
@@ -35391,7 +35394,7 @@
         <v>1</v>
       </c>
       <c r="I446" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J446" t="n">
         <v>11086</v>
@@ -35412,7 +35415,7 @@
         <v>86</v>
       </c>
       <c r="P446" t="n">
-        <v>11076</v>
+        <v>11074</v>
       </c>
       <c r="Q446" t="n">
         <v>1</v>
@@ -35450,10 +35453,10 @@
         <v>167</v>
       </c>
       <c r="D447" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E447" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F447" t="s">
         <v>85</v>
@@ -35465,7 +35468,7 @@
         <v>1</v>
       </c>
       <c r="I447" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J447" t="n">
         <v>11086</v>
@@ -35524,10 +35527,10 @@
         <v>168</v>
       </c>
       <c r="D448" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E448" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F448" t="s">
         <v>85</v>
@@ -35539,7 +35542,7 @@
         <v>1</v>
       </c>
       <c r="I448" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J448" t="n">
         <v>11086</v>
@@ -35560,7 +35563,7 @@
         <v>86</v>
       </c>
       <c r="P448" t="n">
-        <v>11068</v>
+        <v>11069</v>
       </c>
       <c r="Q448" t="n">
         <v>1</v>
@@ -35598,10 +35601,10 @@
         <v>169</v>
       </c>
       <c r="D449" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E449" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F449" t="s">
         <v>85</v>
@@ -35613,7 +35616,7 @@
         <v>1</v>
       </c>
       <c r="I449" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J449" t="n">
         <v>11086</v>
@@ -35634,7 +35637,7 @@
         <v>86</v>
       </c>
       <c r="P449" t="n">
-        <v>11074</v>
+        <v>11075</v>
       </c>
       <c r="Q449" t="n">
         <v>1</v>
@@ -35672,10 +35675,10 @@
         <v>170</v>
       </c>
       <c r="D450" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E450" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F450" t="s">
         <v>85</v>
@@ -35687,7 +35690,7 @@
         <v>1</v>
       </c>
       <c r="I450" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J450" t="n">
         <v>11086</v>
@@ -35746,10 +35749,10 @@
         <v>171</v>
       </c>
       <c r="D451" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E451" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F451" t="s">
         <v>85</v>
@@ -35761,7 +35764,7 @@
         <v>1</v>
       </c>
       <c r="I451" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J451" t="n">
         <v>11086</v>
@@ -35820,10 +35823,10 @@
         <v>172</v>
       </c>
       <c r="D452" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E452" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F452" t="s">
         <v>85</v>
@@ -35835,7 +35838,7 @@
         <v>1</v>
       </c>
       <c r="I452" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J452" t="n">
         <v>11086</v>
@@ -35894,10 +35897,10 @@
         <v>173</v>
       </c>
       <c r="D453" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E453" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F453" t="s">
         <v>85</v>
@@ -35909,7 +35912,7 @@
         <v>1</v>
       </c>
       <c r="I453" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J453" t="n">
         <v>11086</v>
@@ -35968,10 +35971,10 @@
         <v>174</v>
       </c>
       <c r="D454" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E454" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F454" t="s">
         <v>85</v>
@@ -35983,7 +35986,7 @@
         <v>1</v>
       </c>
       <c r="I454" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J454" t="n">
         <v>11086</v>
@@ -36042,10 +36045,10 @@
         <v>175</v>
       </c>
       <c r="D455" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E455" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F455" t="s">
         <v>85</v>
@@ -36057,7 +36060,7 @@
         <v>1</v>
       </c>
       <c r="I455" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J455" t="n">
         <v>11086</v>
@@ -36078,7 +36081,7 @@
         <v>86</v>
       </c>
       <c r="P455" t="n">
-        <v>11061</v>
+        <v>11062</v>
       </c>
       <c r="Q455" t="n">
         <v>1</v>
@@ -36116,10 +36119,10 @@
         <v>176</v>
       </c>
       <c r="D456" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E456" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F456" t="s">
         <v>85</v>
@@ -36131,7 +36134,7 @@
         <v>1</v>
       </c>
       <c r="I456" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J456" t="n">
         <v>11086</v>
@@ -36152,7 +36155,7 @@
         <v>86</v>
       </c>
       <c r="P456" t="n">
-        <v>11063</v>
+        <v>11062</v>
       </c>
       <c r="Q456" t="n">
         <v>1</v>
@@ -36190,10 +36193,10 @@
         <v>182</v>
       </c>
       <c r="D457" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E457" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F457" t="s">
         <v>85</v>
@@ -36205,7 +36208,7 @@
         <v>1</v>
       </c>
       <c r="I457" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J457" t="n">
         <v>11086</v>
@@ -36214,7 +36217,7 @@
         <v>1</v>
       </c>
       <c r="L457" t="n">
-        <v>5.90865062670669e-257</v>
+        <v>4.61101050499739e-258</v>
       </c>
       <c r="M457" t="n">
         <v>1</v>
@@ -36264,10 +36267,10 @@
         <v>183</v>
       </c>
       <c r="D458" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E458" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F458" t="s">
         <v>85</v>
@@ -36279,7 +36282,7 @@
         <v>1</v>
       </c>
       <c r="I458" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J458" t="n">
         <v>11086</v>
@@ -36338,10 +36341,10 @@
         <v>184</v>
       </c>
       <c r="D459" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E459" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F459" t="s">
         <v>85</v>
@@ -36353,7 +36356,7 @@
         <v>1</v>
       </c>
       <c r="I459" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J459" t="n">
         <v>11086</v>
@@ -36362,7 +36365,7 @@
         <v>1</v>
       </c>
       <c r="L459" t="n">
-        <v>4.33768448179932e-248</v>
+        <v>1.10891769674042e-254</v>
       </c>
       <c r="M459" t="n">
         <v>1</v>
@@ -36412,10 +36415,10 @@
         <v>185</v>
       </c>
       <c r="D460" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E460" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F460" t="s">
         <v>85</v>
@@ -36427,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="I460" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J460" t="n">
         <v>11086</v>
@@ -36436,7 +36439,7 @@
         <v>1</v>
       </c>
       <c r="L460" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000126038915898367</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000374410466496174</v>
       </c>
       <c r="M460" t="n">
         <v>1</v>
@@ -36486,10 +36489,10 @@
         <v>186</v>
       </c>
       <c r="D461" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E461" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F461" t="s">
         <v>85</v>
@@ -36501,7 +36504,7 @@
         <v>1</v>
       </c>
       <c r="I461" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J461" t="n">
         <v>11086</v>
@@ -36510,7 +36513,7 @@
         <v>1</v>
       </c>
       <c r="L461" t="n">
-        <v>1.99698964510116e-264</v>
+        <v>3.94928060593507e-267</v>
       </c>
       <c r="M461" t="n">
         <v>1</v>
@@ -36560,10 +36563,10 @@
         <v>187</v>
       </c>
       <c r="D462" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E462" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F462" t="s">
         <v>85</v>
@@ -36575,7 +36578,7 @@
         <v>1</v>
       </c>
       <c r="I462" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J462" t="n">
         <v>11086</v>
@@ -36584,7 +36587,7 @@
         <v>1</v>
       </c>
       <c r="L462" t="n">
-        <v>9.94587737505964e-256</v>
+        <v>4.54736356637523e-261</v>
       </c>
       <c r="M462" t="n">
         <v>1</v>
@@ -36634,10 +36637,10 @@
         <v>188</v>
       </c>
       <c r="D463" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E463" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F463" t="s">
         <v>85</v>
@@ -36649,7 +36652,7 @@
         <v>1</v>
       </c>
       <c r="I463" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J463" t="n">
         <v>11086</v>
@@ -36658,7 +36661,7 @@
         <v>1</v>
       </c>
       <c r="L463" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000146203144425831</v>
+        <v>6.7215862410312e-206</v>
       </c>
       <c r="M463" t="n">
         <v>1</v>
@@ -36708,10 +36711,10 @@
         <v>189</v>
       </c>
       <c r="D464" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E464" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F464" t="s">
         <v>85</v>
@@ -36723,7 +36726,7 @@
         <v>1</v>
       </c>
       <c r="I464" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J464" t="n">
         <v>11086</v>
@@ -36732,7 +36735,7 @@
         <v>1</v>
       </c>
       <c r="L464" t="n">
-        <v>1.96804270661297e-221</v>
+        <v>3.08535257595302e-228</v>
       </c>
       <c r="M464" t="n">
         <v>1</v>
@@ -36744,7 +36747,7 @@
         <v>86</v>
       </c>
       <c r="P464" t="n">
-        <v>11064</v>
+        <v>11063</v>
       </c>
       <c r="Q464" t="n">
         <v>1</v>
@@ -36782,10 +36785,10 @@
         <v>190</v>
       </c>
       <c r="D465" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E465" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F465" t="s">
         <v>85</v>
@@ -36797,7 +36800,7 @@
         <v>1</v>
       </c>
       <c r="I465" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J465" t="n">
         <v>11086</v>
@@ -36806,7 +36809,7 @@
         <v>1</v>
       </c>
       <c r="L465" t="n">
-        <v>1.97626258336499e-323</v>
+        <v>0</v>
       </c>
       <c r="M465" t="n">
         <v>1</v>
@@ -36856,10 +36859,10 @@
         <v>191</v>
       </c>
       <c r="D466" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E466" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F466" t="s">
         <v>85</v>
@@ -36871,7 +36874,7 @@
         <v>1</v>
       </c>
       <c r="I466" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J466" t="n">
         <v>11086</v>
@@ -36880,7 +36883,7 @@
         <v>1</v>
       </c>
       <c r="L466" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000565507935104582</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000257400885328575</v>
       </c>
       <c r="M466" t="n">
         <v>1</v>
@@ -36930,10 +36933,10 @@
         <v>192</v>
       </c>
       <c r="D467" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E467" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F467" t="s">
         <v>85</v>
@@ -36945,7 +36948,7 @@
         <v>1</v>
       </c>
       <c r="I467" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J467" t="n">
         <v>11086</v>
@@ -36966,7 +36969,7 @@
         <v>86</v>
       </c>
       <c r="P467" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
       <c r="Q467" t="n">
         <v>1</v>
@@ -37004,10 +37007,10 @@
         <v>193</v>
       </c>
       <c r="D468" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E468" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F468" t="s">
         <v>85</v>
@@ -37019,7 +37022,7 @@
         <v>1</v>
       </c>
       <c r="I468" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J468" t="n">
         <v>11086</v>
@@ -37040,7 +37043,7 @@
         <v>86</v>
       </c>
       <c r="P468" t="n">
-        <v>11066</v>
+        <v>11065</v>
       </c>
       <c r="Q468" t="n">
         <v>1</v>
@@ -37078,10 +37081,10 @@
         <v>194</v>
       </c>
       <c r="D469" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E469" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F469" t="s">
         <v>85</v>
@@ -37093,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="I469" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J469" t="n">
         <v>11086</v>
@@ -37152,10 +37155,10 @@
         <v>195</v>
       </c>
       <c r="D470" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E470" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F470" t="s">
         <v>85</v>
@@ -37167,7 +37170,7 @@
         <v>1</v>
       </c>
       <c r="I470" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J470" t="n">
         <v>11086</v>
@@ -37226,10 +37229,10 @@
         <v>196</v>
       </c>
       <c r="D471" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E471" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F471" t="s">
         <v>85</v>
@@ -37241,7 +37244,7 @@
         <v>1</v>
       </c>
       <c r="I471" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J471" t="n">
         <v>11086</v>
@@ -37300,10 +37303,10 @@
         <v>197</v>
       </c>
       <c r="D472" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E472" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F472" t="s">
         <v>85</v>
@@ -37315,7 +37318,7 @@
         <v>1</v>
       </c>
       <c r="I472" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J472" t="n">
         <v>11086</v>
@@ -37374,10 +37377,10 @@
         <v>198</v>
       </c>
       <c r="D473" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E473" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F473" t="s">
         <v>85</v>
@@ -37389,7 +37392,7 @@
         <v>1</v>
       </c>
       <c r="I473" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J473" t="n">
         <v>11086</v>
@@ -37398,7 +37401,7 @@
         <v>1</v>
       </c>
       <c r="L473" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000348323963406674</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000564617454336252</v>
       </c>
       <c r="M473" t="n">
         <v>1</v>
@@ -37410,7 +37413,7 @@
         <v>86</v>
       </c>
       <c r="P473" t="n">
-        <v>11068</v>
+        <v>11067</v>
       </c>
       <c r="Q473" t="n">
         <v>1</v>
@@ -37448,10 +37451,10 @@
         <v>199</v>
       </c>
       <c r="D474" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E474" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F474" t="s">
         <v>85</v>
@@ -37463,7 +37466,7 @@
         <v>1</v>
       </c>
       <c r="I474" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J474" t="n">
         <v>11086</v>
@@ -37472,7 +37475,7 @@
         <v>1</v>
       </c>
       <c r="L474" t="n">
-        <v>2.03285808618971e-218</v>
+        <v>1.81307650128352e-222</v>
       </c>
       <c r="M474" t="n">
         <v>1</v>
@@ -37522,10 +37525,10 @@
         <v>200</v>
       </c>
       <c r="D475" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E475" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F475" t="s">
         <v>85</v>
@@ -37537,7 +37540,7 @@
         <v>1</v>
       </c>
       <c r="I475" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J475" t="n">
         <v>11086</v>
@@ -37546,7 +37549,7 @@
         <v>1</v>
       </c>
       <c r="L475" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000270054133150429</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000188466636022143</v>
       </c>
       <c r="M475" t="n">
         <v>1</v>
@@ -37596,10 +37599,10 @@
         <v>201</v>
       </c>
       <c r="D476" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E476" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F476" t="s">
         <v>85</v>
@@ -37611,7 +37614,7 @@
         <v>1</v>
       </c>
       <c r="I476" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J476" t="n">
         <v>11086</v>
@@ -37620,7 +37623,7 @@
         <v>1</v>
       </c>
       <c r="L476" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000843687647676931</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000606152993943124</v>
       </c>
       <c r="M476" t="n">
         <v>1</v>
@@ -37632,7 +37635,7 @@
         <v>86</v>
       </c>
       <c r="P476" t="n">
-        <v>11065</v>
+        <v>11066</v>
       </c>
       <c r="Q476" t="n">
         <v>1</v>
@@ -37670,10 +37673,10 @@
         <v>202</v>
       </c>
       <c r="D477" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E477" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F477" t="s">
         <v>85</v>
@@ -37685,7 +37688,7 @@
         <v>1</v>
       </c>
       <c r="I477" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J477" t="n">
         <v>11086</v>
@@ -37694,7 +37697,7 @@
         <v>1</v>
       </c>
       <c r="L477" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000859787333580503</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000292782575903692</v>
       </c>
       <c r="M477" t="n">
         <v>1</v>
@@ -37744,10 +37747,10 @@
         <v>203</v>
       </c>
       <c r="D478" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E478" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F478" t="s">
         <v>85</v>
@@ -37759,7 +37762,7 @@
         <v>1</v>
       </c>
       <c r="I478" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J478" t="n">
         <v>11086</v>
@@ -37768,7 +37771,7 @@
         <v>1</v>
       </c>
       <c r="L478" t="n">
-        <v>1.92449176751061e-240</v>
+        <v>2.17674951604577e-243</v>
       </c>
       <c r="M478" t="n">
         <v>1</v>
@@ -37818,10 +37821,10 @@
         <v>204</v>
       </c>
       <c r="D479" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E479" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F479" t="s">
         <v>85</v>
@@ -37833,7 +37836,7 @@
         <v>1</v>
       </c>
       <c r="I479" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J479" t="n">
         <v>11086</v>
@@ -37842,7 +37845,7 @@
         <v>1</v>
       </c>
       <c r="L479" t="n">
-        <v>3.65388154461582e-268</v>
+        <v>1.24101050920951e-273</v>
       </c>
       <c r="M479" t="n">
         <v>1</v>
@@ -37892,10 +37895,10 @@
         <v>205</v>
       </c>
       <c r="D480" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E480" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F480" t="s">
         <v>85</v>
@@ -37907,7 +37910,7 @@
         <v>1</v>
       </c>
       <c r="I480" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J480" t="n">
         <v>11086</v>
@@ -37916,7 +37919,7 @@
         <v>1</v>
       </c>
       <c r="L480" t="n">
-        <v>4.99929515125049e-296</v>
+        <v>3.05838543267793e-296</v>
       </c>
       <c r="M480" t="n">
         <v>1</v>
@@ -37966,10 +37969,10 @@
         <v>206</v>
       </c>
       <c r="D481" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E481" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F481" t="s">
         <v>85</v>
@@ -37981,7 +37984,7 @@
         <v>1</v>
       </c>
       <c r="I481" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J481" t="n">
         <v>11086</v>
@@ -37990,7 +37993,7 @@
         <v>1</v>
       </c>
       <c r="L481" t="n">
-        <v>9.78189680272574e-291</v>
+        <v>3.80894250204508e-294</v>
       </c>
       <c r="M481" t="n">
         <v>1</v>
@@ -38002,7 +38005,7 @@
         <v>86</v>
       </c>
       <c r="P481" t="n">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="Q481" t="n">
         <v>1</v>
@@ -38040,10 +38043,10 @@
         <v>207</v>
       </c>
       <c r="D482" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E482" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F482" t="s">
         <v>85</v>
@@ -38055,7 +38058,7 @@
         <v>1</v>
       </c>
       <c r="I482" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J482" t="n">
         <v>11086</v>
@@ -38064,7 +38067,7 @@
         <v>1</v>
       </c>
       <c r="L482" t="n">
-        <v>8.56320132441447e-219</v>
+        <v>1.58045135701408e-223</v>
       </c>
       <c r="M482" t="n">
         <v>1</v>
@@ -38114,10 +38117,10 @@
         <v>208</v>
       </c>
       <c r="D483" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E483" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F483" t="s">
         <v>85</v>
@@ -38129,7 +38132,7 @@
         <v>1</v>
       </c>
       <c r="I483" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J483" t="n">
         <v>11086</v>
@@ -38188,10 +38191,10 @@
         <v>209</v>
       </c>
       <c r="D484" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E484" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F484" t="s">
         <v>85</v>
@@ -38203,7 +38206,7 @@
         <v>1</v>
       </c>
       <c r="I484" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J484" t="n">
         <v>11086</v>
@@ -38224,7 +38227,7 @@
         <v>86</v>
       </c>
       <c r="P484" t="n">
-        <v>11019</v>
+        <v>11018</v>
       </c>
       <c r="Q484" t="n">
         <v>1</v>
@@ -38262,10 +38265,10 @@
         <v>210</v>
       </c>
       <c r="D485" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E485" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F485" t="s">
         <v>85</v>
@@ -38277,7 +38280,7 @@
         <v>1</v>
       </c>
       <c r="I485" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J485" t="n">
         <v>11086</v>
@@ -38286,7 +38289,7 @@
         <v>1</v>
       </c>
       <c r="L485" t="n">
-        <v>1.77630141368081e-280</v>
+        <v>8.94157872567483e-285</v>
       </c>
       <c r="M485" t="n">
         <v>1</v>
@@ -38336,10 +38339,10 @@
         <v>211</v>
       </c>
       <c r="D486" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E486" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F486" t="s">
         <v>85</v>
@@ -38351,7 +38354,7 @@
         <v>1</v>
       </c>
       <c r="I486" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J486" t="n">
         <v>11086</v>
@@ -38360,7 +38363,7 @@
         <v>1</v>
       </c>
       <c r="L486" t="n">
-        <v>2.08263301424516e-276</v>
+        <v>3.36200651469688e-284</v>
       </c>
       <c r="M486" t="n">
         <v>1</v>
@@ -38372,7 +38375,7 @@
         <v>86</v>
       </c>
       <c r="P486" t="n">
-        <v>11059</v>
+        <v>11058</v>
       </c>
       <c r="Q486" t="n">
         <v>1</v>
@@ -38410,10 +38413,10 @@
         <v>212</v>
       </c>
       <c r="D487" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E487" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F487" t="s">
         <v>85</v>
@@ -38425,7 +38428,7 @@
         <v>1</v>
       </c>
       <c r="I487" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J487" t="n">
         <v>11086</v>
@@ -38446,7 +38449,7 @@
         <v>86</v>
       </c>
       <c r="P487" t="n">
-        <v>11064</v>
+        <v>11065</v>
       </c>
       <c r="Q487" t="n">
         <v>1</v>
@@ -38484,10 +38487,10 @@
         <v>213</v>
       </c>
       <c r="D488" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E488" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F488" t="s">
         <v>85</v>
@@ -38499,7 +38502,7 @@
         <v>1</v>
       </c>
       <c r="I488" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J488" t="n">
         <v>11086</v>
@@ -38558,10 +38561,10 @@
         <v>214</v>
       </c>
       <c r="D489" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E489" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F489" t="s">
         <v>85</v>
@@ -38573,7 +38576,7 @@
         <v>1</v>
       </c>
       <c r="I489" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J489" t="n">
         <v>11086</v>
@@ -38582,7 +38585,7 @@
         <v>1</v>
       </c>
       <c r="L489" t="n">
-        <v>3.70549234380935e-322</v>
+        <v>2.27270197086973e-322</v>
       </c>
       <c r="M489" t="n">
         <v>1</v>
@@ -38594,7 +38597,7 @@
         <v>86</v>
       </c>
       <c r="P489" t="n">
-        <v>11051</v>
+        <v>11053</v>
       </c>
       <c r="Q489" t="n">
         <v>1</v>
@@ -38632,10 +38635,10 @@
         <v>215</v>
       </c>
       <c r="D490" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E490" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F490" t="s">
         <v>85</v>
@@ -38647,7 +38650,7 @@
         <v>1</v>
       </c>
       <c r="I490" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J490" t="n">
         <v>11086</v>
@@ -38656,7 +38659,7 @@
         <v>1</v>
       </c>
       <c r="L490" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000509711079738064</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000109716747313391</v>
       </c>
       <c r="M490" t="n">
         <v>1</v>
@@ -38668,7 +38671,7 @@
         <v>86</v>
       </c>
       <c r="P490" t="n">
-        <v>11037</v>
+        <v>11035</v>
       </c>
       <c r="Q490" t="n">
         <v>1</v>
@@ -38706,10 +38709,10 @@
         <v>216</v>
       </c>
       <c r="D491" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E491" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F491" t="s">
         <v>85</v>
@@ -38721,7 +38724,7 @@
         <v>1</v>
       </c>
       <c r="I491" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J491" t="n">
         <v>11086</v>
@@ -38742,7 +38745,7 @@
         <v>86</v>
       </c>
       <c r="P491" t="n">
-        <v>11071</v>
+        <v>11069</v>
       </c>
       <c r="Q491" t="n">
         <v>1</v>
@@ -38780,10 +38783,10 @@
         <v>217</v>
       </c>
       <c r="D492" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E492" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F492" t="s">
         <v>85</v>
@@ -38795,7 +38798,7 @@
         <v>1</v>
       </c>
       <c r="I492" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J492" t="n">
         <v>11086</v>
@@ -38804,7 +38807,7 @@
         <v>1</v>
       </c>
       <c r="L492" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000715211343570906</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000771865840634348</v>
       </c>
       <c r="M492" t="n">
         <v>1</v>
@@ -38854,10 +38857,10 @@
         <v>218</v>
       </c>
       <c r="D493" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E493" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F493" t="s">
         <v>85</v>
@@ -38869,7 +38872,7 @@
         <v>1</v>
       </c>
       <c r="I493" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J493" t="n">
         <v>11086</v>
@@ -38878,7 +38881,7 @@
         <v>1</v>
       </c>
       <c r="L493" t="n">
-        <v>1.13959037870964e-242</v>
+        <v>3.45595351381137e-241</v>
       </c>
       <c r="M493" t="n">
         <v>1</v>
@@ -38890,7 +38893,7 @@
         <v>86</v>
       </c>
       <c r="P493" t="n">
-        <v>11052</v>
+        <v>11053</v>
       </c>
       <c r="Q493" t="n">
         <v>1</v>
@@ -38928,10 +38931,10 @@
         <v>219</v>
       </c>
       <c r="D494" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E494" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F494" t="s">
         <v>85</v>
@@ -38943,7 +38946,7 @@
         <v>1</v>
       </c>
       <c r="I494" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J494" t="n">
         <v>11086</v>
@@ -38952,7 +38955,7 @@
         <v>1</v>
       </c>
       <c r="L494" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000230759065173658</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000859288557310002</v>
       </c>
       <c r="M494" t="n">
         <v>1</v>
@@ -39002,10 +39005,10 @@
         <v>220</v>
       </c>
       <c r="D495" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E495" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F495" t="s">
         <v>85</v>
@@ -39017,7 +39020,7 @@
         <v>1</v>
       </c>
       <c r="I495" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J495" t="n">
         <v>11086</v>
@@ -39026,7 +39029,7 @@
         <v>1</v>
       </c>
       <c r="L495" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000142449090082117</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000105774139568979</v>
       </c>
       <c r="M495" t="n">
         <v>1</v>
@@ -39038,7 +39041,7 @@
         <v>86</v>
       </c>
       <c r="P495" t="n">
-        <v>11056</v>
+        <v>11054</v>
       </c>
       <c r="Q495" t="n">
         <v>1</v>
@@ -39076,10 +39079,10 @@
         <v>221</v>
       </c>
       <c r="D496" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E496" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F496" t="s">
         <v>85</v>
@@ -39091,7 +39094,7 @@
         <v>1</v>
       </c>
       <c r="I496" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J496" t="n">
         <v>11086</v>
@@ -39100,7 +39103,7 @@
         <v>1</v>
       </c>
       <c r="L496" t="n">
-        <v>1.04739128515513e-207</v>
+        <v>4.04504722865865e-207</v>
       </c>
       <c r="M496" t="n">
         <v>1</v>
@@ -39112,7 +39115,7 @@
         <v>86</v>
       </c>
       <c r="P496" t="n">
-        <v>11052</v>
+        <v>11051</v>
       </c>
       <c r="Q496" t="n">
         <v>1</v>
@@ -39150,10 +39153,10 @@
         <v>222</v>
       </c>
       <c r="D497" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E497" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F497" t="s">
         <v>85</v>
@@ -39165,7 +39168,7 @@
         <v>1</v>
       </c>
       <c r="I497" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J497" t="n">
         <v>11086</v>
@@ -39224,10 +39227,10 @@
         <v>223</v>
       </c>
       <c r="D498" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E498" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F498" t="s">
         <v>85</v>
@@ -39239,7 +39242,7 @@
         <v>1</v>
       </c>
       <c r="I498" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J498" t="n">
         <v>11086</v>
@@ -39298,10 +39301,10 @@
         <v>224</v>
       </c>
       <c r="D499" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E499" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F499" t="s">
         <v>85</v>
@@ -39313,7 +39316,7 @@
         <v>1</v>
       </c>
       <c r="I499" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J499" t="n">
         <v>11086</v>
@@ -39372,10 +39375,10 @@
         <v>225</v>
       </c>
       <c r="D500" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E500" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F500" t="s">
         <v>85</v>
@@ -39387,7 +39390,7 @@
         <v>1</v>
       </c>
       <c r="I500" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J500" t="n">
         <v>11086</v>
@@ -39408,7 +39411,7 @@
         <v>86</v>
       </c>
       <c r="P500" t="n">
-        <v>11067</v>
+        <v>11066</v>
       </c>
       <c r="Q500" t="n">
         <v>1</v>
@@ -39446,10 +39449,10 @@
         <v>226</v>
       </c>
       <c r="D501" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E501" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F501" t="s">
         <v>85</v>
@@ -39461,7 +39464,7 @@
         <v>1</v>
       </c>
       <c r="I501" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J501" t="n">
         <v>11086</v>
@@ -39482,7 +39485,7 @@
         <v>86</v>
       </c>
       <c r="P501" t="n">
-        <v>10176</v>
+        <v>10171</v>
       </c>
       <c r="Q501" t="n">
         <v>1</v>
@@ -39520,10 +39523,10 @@
         <v>227</v>
       </c>
       <c r="D502" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E502" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F502" t="s">
         <v>85</v>
@@ -39535,7 +39538,7 @@
         <v>1</v>
       </c>
       <c r="I502" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J502" t="n">
         <v>11086</v>
@@ -39556,7 +39559,7 @@
         <v>86</v>
       </c>
       <c r="P502" t="n">
-        <v>11014</v>
+        <v>11015</v>
       </c>
       <c r="Q502" t="n">
         <v>1</v>
@@ -39594,10 +39597,10 @@
         <v>228</v>
       </c>
       <c r="D503" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E503" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F503" t="s">
         <v>85</v>
@@ -39609,7 +39612,7 @@
         <v>1</v>
       </c>
       <c r="I503" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J503" t="n">
         <v>11086</v>
@@ -39668,10 +39671,10 @@
         <v>229</v>
       </c>
       <c r="D504" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E504" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F504" t="s">
         <v>85</v>
@@ -39683,7 +39686,7 @@
         <v>1</v>
       </c>
       <c r="I504" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J504" t="n">
         <v>11086</v>
@@ -39704,7 +39707,7 @@
         <v>86</v>
       </c>
       <c r="P504" t="n">
-        <v>11074</v>
+        <v>11072</v>
       </c>
       <c r="Q504" t="n">
         <v>1</v>
@@ -39742,10 +39745,10 @@
         <v>230</v>
       </c>
       <c r="D505" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E505" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F505" t="s">
         <v>85</v>
@@ -39757,7 +39760,7 @@
         <v>1</v>
       </c>
       <c r="I505" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J505" t="n">
         <v>11086</v>
@@ -39778,7 +39781,7 @@
         <v>86</v>
       </c>
       <c r="P505" t="n">
-        <v>11044</v>
+        <v>11043</v>
       </c>
       <c r="Q505" t="n">
         <v>1</v>
@@ -39816,10 +39819,10 @@
         <v>231</v>
       </c>
       <c r="D506" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E506" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F506" t="s">
         <v>85</v>
@@ -39831,7 +39834,7 @@
         <v>1</v>
       </c>
       <c r="I506" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J506" t="n">
         <v>11086</v>
@@ -39852,7 +39855,7 @@
         <v>86</v>
       </c>
       <c r="P506" t="n">
-        <v>11061</v>
+        <v>11062</v>
       </c>
       <c r="Q506" t="n">
         <v>1</v>
@@ -39890,10 +39893,10 @@
         <v>232</v>
       </c>
       <c r="D507" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E507" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F507" t="s">
         <v>85</v>
@@ -39905,7 +39908,7 @@
         <v>1</v>
       </c>
       <c r="I507" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J507" t="n">
         <v>11086</v>
@@ -39914,7 +39917,7 @@
         <v>1</v>
       </c>
       <c r="L507" t="n">
-        <v>1.21144873493178e-279</v>
+        <v>1.73284871646445e-283</v>
       </c>
       <c r="M507" t="n">
         <v>1</v>
@@ -39964,10 +39967,10 @@
         <v>233</v>
       </c>
       <c r="D508" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E508" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F508" t="s">
         <v>85</v>
@@ -39979,7 +39982,7 @@
         <v>1</v>
       </c>
       <c r="I508" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J508" t="n">
         <v>11086</v>
@@ -39988,7 +39991,7 @@
         <v>1</v>
       </c>
       <c r="L508" t="n">
-        <v>2.6311879393317e-291</v>
+        <v>1.36009561543999e-286</v>
       </c>
       <c r="M508" t="n">
         <v>1</v>
@@ -40038,10 +40041,10 @@
         <v>234</v>
       </c>
       <c r="D509" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E509" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F509" t="s">
         <v>85</v>
@@ -40053,7 +40056,7 @@
         <v>1</v>
       </c>
       <c r="I509" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J509" t="n">
         <v>11086</v>
@@ -40062,7 +40065,7 @@
         <v>1</v>
       </c>
       <c r="L509" t="n">
-        <v>3.28007485904316e-245</v>
+        <v>4.36835794524717e-244</v>
       </c>
       <c r="M509" t="n">
         <v>1</v>
@@ -40112,10 +40115,10 @@
         <v>235</v>
       </c>
       <c r="D510" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E510" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F510" t="s">
         <v>85</v>
@@ -40127,7 +40130,7 @@
         <v>1</v>
       </c>
       <c r="I510" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J510" t="n">
         <v>11086</v>
@@ -40136,7 +40139,7 @@
         <v>1</v>
       </c>
       <c r="L510" t="n">
-        <v>1.19478795912842e-250</v>
+        <v>9.07085888662292e-253</v>
       </c>
       <c r="M510" t="n">
         <v>1</v>
@@ -40186,10 +40189,10 @@
         <v>236</v>
       </c>
       <c r="D511" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E511" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F511" t="s">
         <v>85</v>
@@ -40201,7 +40204,7 @@
         <v>1</v>
       </c>
       <c r="I511" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J511" t="n">
         <v>11086</v>
@@ -40210,7 +40213,7 @@
         <v>1</v>
       </c>
       <c r="L511" t="n">
-        <v>9.8477271616664e-268</v>
+        <v>2.92824284594137e-271</v>
       </c>
       <c r="M511" t="n">
         <v>1</v>
@@ -40222,7 +40225,7 @@
         <v>86</v>
       </c>
       <c r="P511" t="n">
-        <v>11059</v>
+        <v>11058</v>
       </c>
       <c r="Q511" t="n">
         <v>1</v>
@@ -40260,10 +40263,10 @@
         <v>237</v>
       </c>
       <c r="D512" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E512" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F512" t="s">
         <v>85</v>
@@ -40275,7 +40278,7 @@
         <v>1</v>
       </c>
       <c r="I512" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J512" t="n">
         <v>11086</v>
@@ -40334,10 +40337,10 @@
         <v>238</v>
       </c>
       <c r="D513" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E513" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F513" t="s">
         <v>85</v>
@@ -40349,7 +40352,7 @@
         <v>1</v>
       </c>
       <c r="I513" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J513" t="n">
         <v>11086</v>
@@ -40370,7 +40373,7 @@
         <v>86</v>
       </c>
       <c r="P513" t="n">
-        <v>11069</v>
+        <v>11068</v>
       </c>
       <c r="Q513" t="n">
         <v>1</v>
@@ -40408,10 +40411,10 @@
         <v>239</v>
       </c>
       <c r="D514" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E514" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F514" t="s">
         <v>85</v>
@@ -40423,7 +40426,7 @@
         <v>1</v>
       </c>
       <c r="I514" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J514" t="n">
         <v>11086</v>
@@ -40444,7 +40447,7 @@
         <v>86</v>
       </c>
       <c r="P514" t="n">
-        <v>11041</v>
+        <v>11040</v>
       </c>
       <c r="Q514" t="n">
         <v>1</v>
@@ -40482,10 +40485,10 @@
         <v>240</v>
       </c>
       <c r="D515" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E515" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F515" t="s">
         <v>85</v>
@@ -40497,7 +40500,7 @@
         <v>1</v>
       </c>
       <c r="I515" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J515" t="n">
         <v>11086</v>
@@ -40518,7 +40521,7 @@
         <v>86</v>
       </c>
       <c r="P515" t="n">
-        <v>11079</v>
+        <v>11078</v>
       </c>
       <c r="Q515" t="n">
         <v>1</v>
@@ -40556,10 +40559,10 @@
         <v>241</v>
       </c>
       <c r="D516" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E516" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F516" t="s">
         <v>85</v>
@@ -40571,7 +40574,7 @@
         <v>1</v>
       </c>
       <c r="I516" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J516" t="n">
         <v>11086</v>
@@ -40630,10 +40633,10 @@
         <v>242</v>
       </c>
       <c r="D517" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E517" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F517" t="s">
         <v>85</v>
@@ -40645,7 +40648,7 @@
         <v>1</v>
       </c>
       <c r="I517" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J517" t="n">
         <v>11086</v>
@@ -40704,10 +40707,10 @@
         <v>243</v>
       </c>
       <c r="D518" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E518" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F518" t="s">
         <v>85</v>
@@ -40719,7 +40722,7 @@
         <v>1</v>
       </c>
       <c r="I518" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J518" t="n">
         <v>11086</v>
@@ -40740,7 +40743,7 @@
         <v>86</v>
       </c>
       <c r="P518" t="n">
-        <v>11044</v>
+        <v>11043</v>
       </c>
       <c r="Q518" t="n">
         <v>1</v>
@@ -40778,10 +40781,10 @@
         <v>244</v>
       </c>
       <c r="D519" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E519" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F519" t="s">
         <v>85</v>
@@ -40793,7 +40796,7 @@
         <v>1</v>
       </c>
       <c r="I519" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J519" t="n">
         <v>11086</v>
@@ -40814,7 +40817,7 @@
         <v>86</v>
       </c>
       <c r="P519" t="n">
-        <v>11063</v>
+        <v>11064</v>
       </c>
       <c r="Q519" t="n">
         <v>1</v>
@@ -40852,10 +40855,10 @@
         <v>245</v>
       </c>
       <c r="D520" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E520" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F520" t="s">
         <v>85</v>
@@ -40867,7 +40870,7 @@
         <v>1</v>
       </c>
       <c r="I520" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J520" t="n">
         <v>11086</v>
@@ -40876,7 +40879,7 @@
         <v>1</v>
       </c>
       <c r="L520" t="n">
-        <v>9.14405162864595e-226</v>
+        <v>5.02535927337495e-231</v>
       </c>
       <c r="M520" t="n">
         <v>1</v>
@@ -40888,7 +40891,7 @@
         <v>86</v>
       </c>
       <c r="P520" t="n">
-        <v>11075</v>
+        <v>11074</v>
       </c>
       <c r="Q520" t="n">
         <v>1</v>
@@ -40926,10 +40929,10 @@
         <v>246</v>
       </c>
       <c r="D521" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E521" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F521" t="s">
         <v>85</v>
@@ -40941,7 +40944,7 @@
         <v>1</v>
       </c>
       <c r="I521" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J521" t="n">
         <v>11086</v>
@@ -41000,10 +41003,10 @@
         <v>247</v>
       </c>
       <c r="D522" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E522" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F522" t="s">
         <v>85</v>
@@ -41015,7 +41018,7 @@
         <v>1</v>
       </c>
       <c r="I522" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J522" t="n">
         <v>11086</v>
@@ -41036,7 +41039,7 @@
         <v>86</v>
       </c>
       <c r="P522" t="n">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="Q522" t="n">
         <v>1</v>
@@ -41074,10 +41077,10 @@
         <v>248</v>
       </c>
       <c r="D523" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E523" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F523" t="s">
         <v>85</v>
@@ -41089,7 +41092,7 @@
         <v>1</v>
       </c>
       <c r="I523" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J523" t="n">
         <v>11086</v>
@@ -41110,7 +41113,7 @@
         <v>86</v>
       </c>
       <c r="P523" t="n">
-        <v>11077</v>
+        <v>11076</v>
       </c>
       <c r="Q523" t="n">
         <v>1</v>
@@ -41148,10 +41151,10 @@
         <v>249</v>
       </c>
       <c r="D524" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E524" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F524" t="s">
         <v>85</v>
@@ -41163,7 +41166,7 @@
         <v>1</v>
       </c>
       <c r="I524" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J524" t="n">
         <v>11086</v>
@@ -41172,7 +41175,7 @@
         <v>1</v>
       </c>
       <c r="L524" t="n">
-        <v>1.13377915672727e-302</v>
+        <v>4.72829903301859e-304</v>
       </c>
       <c r="M524" t="n">
         <v>1</v>
@@ -41222,10 +41225,10 @@
         <v>250</v>
       </c>
       <c r="D525" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E525" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F525" t="s">
         <v>85</v>
@@ -41237,7 +41240,7 @@
         <v>1</v>
       </c>
       <c r="I525" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J525" t="n">
         <v>11086</v>
@@ -41296,10 +41299,10 @@
         <v>251</v>
       </c>
       <c r="D526" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E526" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F526" t="s">
         <v>85</v>
@@ -41311,7 +41314,7 @@
         <v>1</v>
       </c>
       <c r="I526" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J526" t="n">
         <v>11086</v>
@@ -41332,7 +41335,7 @@
         <v>86</v>
       </c>
       <c r="P526" t="n">
-        <v>11055</v>
+        <v>11054</v>
       </c>
       <c r="Q526" t="n">
         <v>1</v>
@@ -41370,10 +41373,10 @@
         <v>257</v>
       </c>
       <c r="D527" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E527" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F527" t="s">
         <v>403</v>
@@ -41385,19 +41388,19 @@
         <v>0</v>
       </c>
       <c r="I527" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J527" t="n">
         <v>11086</v>
       </c>
       <c r="K527" t="n">
-        <v>0.999999999721203</v>
+        <v>0.999967206339303</v>
       </c>
       <c r="L527" t="n">
-        <v>0.000000000278797024181194</v>
+        <v>0.0000327936606966705</v>
       </c>
       <c r="M527" t="n">
-        <v>0.999999999442406</v>
+        <v>0.999934412678607</v>
       </c>
       <c r="N527" t="s">
         <v>85</v>
@@ -41406,7 +41409,7 @@
         <v>86</v>
       </c>
       <c r="P527" t="n">
-        <v>11055</v>
+        <v>11057</v>
       </c>
       <c r="Q527" t="n">
         <v>0.166666666666667</v>
@@ -41444,10 +41447,10 @@
         <v>258</v>
       </c>
       <c r="D528" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E528" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F528" t="s">
         <v>403</v>
@@ -41459,19 +41462,19 @@
         <v>0</v>
       </c>
       <c r="I528" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J528" t="n">
         <v>11086</v>
       </c>
       <c r="K528" t="n">
-        <v>0.999999999993608</v>
+        <v>1</v>
       </c>
       <c r="L528" t="n">
-        <v>0.00000000000639198238037078</v>
+        <v>0.00000000000000000121998659532908</v>
       </c>
       <c r="M528" t="n">
-        <v>0.999999999987216</v>
+        <v>1</v>
       </c>
       <c r="N528" t="s">
         <v>85</v>
@@ -41480,7 +41483,7 @@
         <v>86</v>
       </c>
       <c r="P528" t="n">
-        <v>11033</v>
+        <v>11032</v>
       </c>
       <c r="Q528" t="n">
         <v>0.5</v>
@@ -41518,10 +41521,10 @@
         <v>259</v>
       </c>
       <c r="D529" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E529" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F529" t="s">
         <v>85</v>
@@ -41533,7 +41536,7 @@
         <v>0</v>
       </c>
       <c r="I529" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J529" t="n">
         <v>11086</v>
@@ -41542,7 +41545,7 @@
         <v>1</v>
       </c>
       <c r="L529" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000160186071058927</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000152586292186542</v>
       </c>
       <c r="M529" t="n">
         <v>1</v>
@@ -41592,10 +41595,10 @@
         <v>260</v>
       </c>
       <c r="D530" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E530" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F530" t="s">
         <v>403</v>
@@ -41607,19 +41610,19 @@
         <v>0</v>
       </c>
       <c r="I530" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J530" t="n">
         <v>11086</v>
       </c>
       <c r="K530" t="n">
-        <v>1</v>
+        <v>0.999999999999861</v>
       </c>
       <c r="L530" t="n">
-        <v>0.00000000000000000000185644396194598</v>
+        <v>0.000000000000139492286238877</v>
       </c>
       <c r="M530" t="n">
-        <v>1</v>
+        <v>0.999999999999721</v>
       </c>
       <c r="N530" t="s">
         <v>85</v>
@@ -41628,7 +41631,7 @@
         <v>86</v>
       </c>
       <c r="P530" t="n">
-        <v>11018</v>
+        <v>11016</v>
       </c>
       <c r="Q530" t="n">
         <v>0.5</v>
@@ -41666,10 +41669,10 @@
         <v>261</v>
       </c>
       <c r="D531" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E531" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F531" t="s">
         <v>403</v>
@@ -41681,7 +41684,7 @@
         <v>0</v>
       </c>
       <c r="I531" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J531" t="n">
         <v>11086</v>
@@ -41690,7 +41693,7 @@
         <v>1</v>
       </c>
       <c r="L531" t="n">
-        <v>0.000000000000000000000134623463183708</v>
+        <v>0.0000000000000000010042510886091</v>
       </c>
       <c r="M531" t="n">
         <v>1</v>
@@ -41740,10 +41743,10 @@
         <v>262</v>
       </c>
       <c r="D532" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E532" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F532" t="s">
         <v>85</v>
@@ -41755,7 +41758,7 @@
         <v>1</v>
       </c>
       <c r="I532" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J532" t="n">
         <v>11086</v>
@@ -41764,7 +41767,7 @@
         <v>1</v>
       </c>
       <c r="L532" t="n">
-        <v>7.31551499948899e-316</v>
+        <v>8.15722143909732e-319</v>
       </c>
       <c r="M532" t="n">
         <v>1</v>
@@ -41814,10 +41817,10 @@
         <v>263</v>
       </c>
       <c r="D533" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E533" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F533" t="s">
         <v>85</v>
@@ -41829,7 +41832,7 @@
         <v>1</v>
       </c>
       <c r="I533" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J533" t="n">
         <v>11086</v>
@@ -41838,7 +41841,7 @@
         <v>1</v>
       </c>
       <c r="L533" t="n">
-        <v>3.45845952088873e-323</v>
+        <v>2.01578783503229e-321</v>
       </c>
       <c r="M533" t="n">
         <v>1</v>
@@ -41888,10 +41891,10 @@
         <v>264</v>
       </c>
       <c r="D534" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E534" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F534" t="s">
         <v>85</v>
@@ -41903,7 +41906,7 @@
         <v>1</v>
       </c>
       <c r="I534" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J534" t="n">
         <v>11086</v>
@@ -41912,7 +41915,7 @@
         <v>1</v>
       </c>
       <c r="L534" t="n">
-        <v>4.06209139881293e-274</v>
+        <v>2.31539789369881e-275</v>
       </c>
       <c r="M534" t="n">
         <v>1</v>
@@ -41962,10 +41965,10 @@
         <v>265</v>
       </c>
       <c r="D535" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E535" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F535" t="s">
         <v>85</v>
@@ -41977,7 +41980,7 @@
         <v>1</v>
       </c>
       <c r="I535" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J535" t="n">
         <v>11086</v>
@@ -41986,7 +41989,7 @@
         <v>1</v>
       </c>
       <c r="L535" t="n">
-        <v>2.49651370843582e-320</v>
+        <v>4.70176583733531e-317</v>
       </c>
       <c r="M535" t="n">
         <v>1</v>
@@ -42036,10 +42039,10 @@
         <v>266</v>
       </c>
       <c r="D536" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E536" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F536" t="s">
         <v>85</v>
@@ -42051,7 +42054,7 @@
         <v>1</v>
       </c>
       <c r="I536" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J536" t="n">
         <v>11086</v>
@@ -42110,10 +42113,10 @@
         <v>274</v>
       </c>
       <c r="D537" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E537" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F537" t="s">
         <v>85</v>
@@ -42125,7 +42128,7 @@
         <v>1</v>
       </c>
       <c r="I537" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J537" t="n">
         <v>11086</v>
@@ -42134,7 +42137,7 @@
         <v>1</v>
       </c>
       <c r="L537" t="n">
-        <v>9.21007824655684e-303</v>
+        <v>1.05018326072679e-307</v>
       </c>
       <c r="M537" t="n">
         <v>1</v>
@@ -42146,7 +42149,7 @@
         <v>86</v>
       </c>
       <c r="P537" t="n">
-        <v>11019</v>
+        <v>11017</v>
       </c>
       <c r="Q537" t="n">
         <v>1</v>
@@ -42184,10 +42187,10 @@
         <v>275</v>
       </c>
       <c r="D538" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E538" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F538" t="s">
         <v>85</v>
@@ -42199,7 +42202,7 @@
         <v>1</v>
       </c>
       <c r="I538" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J538" t="n">
         <v>11086</v>
@@ -42208,7 +42211,7 @@
         <v>1</v>
       </c>
       <c r="L538" t="n">
-        <v>0.0000000000000000000000000000000171726521917523</v>
+        <v>0.000000000000000000000000000000000000000240616771985661</v>
       </c>
       <c r="M538" t="n">
         <v>1</v>
@@ -42258,10 +42261,10 @@
         <v>276</v>
       </c>
       <c r="D539" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E539" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F539" t="s">
         <v>403</v>
@@ -42273,7 +42276,7 @@
         <v>0</v>
       </c>
       <c r="I539" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J539" t="n">
         <v>11086</v>
@@ -42282,7 +42285,7 @@
         <v>1</v>
       </c>
       <c r="L539" t="n">
-        <v>0.00000000000000000000000228557844412919</v>
+        <v>0.00000000000000000000000000000000174570709434738</v>
       </c>
       <c r="M539" t="n">
         <v>1</v>
@@ -42294,7 +42297,7 @@
         <v>86</v>
       </c>
       <c r="P539" t="n">
-        <v>11055</v>
+        <v>11052</v>
       </c>
       <c r="Q539" t="n">
         <v>0.5</v>
@@ -42332,10 +42335,10 @@
         <v>277</v>
       </c>
       <c r="D540" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E540" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F540" t="s">
         <v>85</v>
@@ -42347,7 +42350,7 @@
         <v>1</v>
       </c>
       <c r="I540" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J540" t="n">
         <v>11086</v>
@@ -42356,7 +42359,7 @@
         <v>1</v>
       </c>
       <c r="L540" t="n">
-        <v>6.7033327109615e-310</v>
+        <v>3.79474505322742e-314</v>
       </c>
       <c r="M540" t="n">
         <v>1</v>
@@ -42368,7 +42371,7 @@
         <v>86</v>
       </c>
       <c r="P540" t="n">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="Q540" t="n">
         <v>1</v>
@@ -42406,10 +42409,10 @@
         <v>278</v>
       </c>
       <c r="D541" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E541" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F541" t="s">
         <v>85</v>
@@ -42421,7 +42424,7 @@
         <v>1</v>
       </c>
       <c r="I541" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J541" t="n">
         <v>11086</v>
@@ -42430,7 +42433,7 @@
         <v>1</v>
       </c>
       <c r="L541" t="n">
-        <v>2.25985626407786e-320</v>
+        <v>0</v>
       </c>
       <c r="M541" t="n">
         <v>1</v>
@@ -42442,7 +42445,7 @@
         <v>86</v>
       </c>
       <c r="P541" t="n">
-        <v>11025</v>
+        <v>11023</v>
       </c>
       <c r="Q541" t="n">
         <v>1</v>
@@ -42480,10 +42483,10 @@
         <v>284</v>
       </c>
       <c r="D542" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E542" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F542" t="s">
         <v>85</v>
@@ -42495,7 +42498,7 @@
         <v>1</v>
       </c>
       <c r="I542" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J542" t="n">
         <v>11086</v>
@@ -42504,7 +42507,7 @@
         <v>1</v>
       </c>
       <c r="L542" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000331931388662739</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000276636637473715</v>
       </c>
       <c r="M542" t="n">
         <v>1</v>
@@ -42516,7 +42519,7 @@
         <v>86</v>
       </c>
       <c r="P542" t="n">
-        <v>11065</v>
+        <v>11063</v>
       </c>
       <c r="Q542" t="n">
         <v>1</v>
@@ -42554,10 +42557,10 @@
         <v>285</v>
       </c>
       <c r="D543" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E543" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F543" t="s">
         <v>85</v>
@@ -42569,7 +42572,7 @@
         <v>1</v>
       </c>
       <c r="I543" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J543" t="n">
         <v>11086</v>
@@ -42578,7 +42581,7 @@
         <v>1</v>
       </c>
       <c r="L543" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000103819267815964</v>
+        <v>1.14634546410409e-206</v>
       </c>
       <c r="M543" t="n">
         <v>1</v>
@@ -42590,7 +42593,7 @@
         <v>86</v>
       </c>
       <c r="P543" t="n">
-        <v>11040</v>
+        <v>11038</v>
       </c>
       <c r="Q543" t="n">
         <v>1</v>
@@ -42628,10 +42631,10 @@
         <v>286</v>
       </c>
       <c r="D544" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E544" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F544" t="s">
         <v>85</v>
@@ -42643,7 +42646,7 @@
         <v>1</v>
       </c>
       <c r="I544" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J544" t="n">
         <v>11086</v>
@@ -42652,7 +42655,7 @@
         <v>1</v>
       </c>
       <c r="L544" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000305133839282656</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000022776379012688</v>
       </c>
       <c r="M544" t="n">
         <v>1</v>
@@ -42664,7 +42667,7 @@
         <v>86</v>
       </c>
       <c r="P544" t="n">
-        <v>11059</v>
+        <v>11057</v>
       </c>
       <c r="Q544" t="n">
         <v>1</v>
@@ -42702,10 +42705,10 @@
         <v>287</v>
       </c>
       <c r="D545" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E545" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F545" t="s">
         <v>85</v>
@@ -42717,7 +42720,7 @@
         <v>1</v>
       </c>
       <c r="I545" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J545" t="n">
         <v>11086</v>
@@ -42726,7 +42729,7 @@
         <v>1</v>
       </c>
       <c r="L545" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000490482266346781</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000144981545903678</v>
       </c>
       <c r="M545" t="n">
         <v>1</v>
@@ -42776,10 +42779,10 @@
         <v>288</v>
       </c>
       <c r="D546" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E546" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F546" t="s">
         <v>85</v>
@@ -42791,7 +42794,7 @@
         <v>1</v>
       </c>
       <c r="I546" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J546" t="n">
         <v>11086</v>
@@ -42800,7 +42803,7 @@
         <v>1</v>
       </c>
       <c r="L546" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000672965036715181</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000697208809240622</v>
       </c>
       <c r="M546" t="n">
         <v>1</v>
@@ -42850,10 +42853,10 @@
         <v>292</v>
       </c>
       <c r="D547" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E547" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F547" t="s">
         <v>85</v>
@@ -42865,7 +42868,7 @@
         <v>1</v>
       </c>
       <c r="I547" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J547" t="n">
         <v>11086</v>
@@ -42874,7 +42877,7 @@
         <v>1</v>
       </c>
       <c r="L547" t="n">
-        <v>1.38121488175902e-215</v>
+        <v>1.75433628362372e-216</v>
       </c>
       <c r="M547" t="n">
         <v>1</v>
@@ -42924,10 +42927,10 @@
         <v>293</v>
       </c>
       <c r="D548" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E548" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F548" t="s">
         <v>85</v>
@@ -42939,7 +42942,7 @@
         <v>1</v>
       </c>
       <c r="I548" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J548" t="n">
         <v>11086</v>
@@ -42998,10 +43001,10 @@
         <v>294</v>
       </c>
       <c r="D549" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E549" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F549" t="s">
         <v>85</v>
@@ -43013,7 +43016,7 @@
         <v>1</v>
       </c>
       <c r="I549" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J549" t="n">
         <v>11086</v>
@@ -43034,7 +43037,7 @@
         <v>86</v>
       </c>
       <c r="P549" t="n">
-        <v>11024</v>
+        <v>11021</v>
       </c>
       <c r="Q549" t="n">
         <v>1</v>
@@ -43072,10 +43075,10 @@
         <v>295</v>
       </c>
       <c r="D550" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E550" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F550" t="s">
         <v>85</v>
@@ -43087,7 +43090,7 @@
         <v>1</v>
       </c>
       <c r="I550" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J550" t="n">
         <v>11086</v>
@@ -43108,7 +43111,7 @@
         <v>86</v>
       </c>
       <c r="P550" t="n">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="Q550" t="n">
         <v>1</v>
@@ -43146,10 +43149,10 @@
         <v>296</v>
       </c>
       <c r="D551" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E551" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F551" t="s">
         <v>85</v>
@@ -43161,7 +43164,7 @@
         <v>1</v>
       </c>
       <c r="I551" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J551" t="n">
         <v>11086</v>
@@ -43182,7 +43185,7 @@
         <v>86</v>
       </c>
       <c r="P551" t="n">
-        <v>11069</v>
+        <v>11068</v>
       </c>
       <c r="Q551" t="n">
         <v>1</v>
@@ -43220,10 +43223,10 @@
         <v>297</v>
       </c>
       <c r="D552" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E552" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F552" t="s">
         <v>85</v>
@@ -43235,7 +43238,7 @@
         <v>1</v>
       </c>
       <c r="I552" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J552" t="n">
         <v>11086</v>
@@ -43294,10 +43297,10 @@
         <v>298</v>
       </c>
       <c r="D553" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E553" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F553" t="s">
         <v>85</v>
@@ -43309,7 +43312,7 @@
         <v>1</v>
       </c>
       <c r="I553" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J553" t="n">
         <v>11086</v>
@@ -43330,7 +43333,7 @@
         <v>86</v>
       </c>
       <c r="P553" t="n">
-        <v>10980</v>
+        <v>10979</v>
       </c>
       <c r="Q553" t="n">
         <v>1</v>
@@ -43368,10 +43371,10 @@
         <v>299</v>
       </c>
       <c r="D554" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E554" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F554" t="s">
         <v>85</v>
@@ -43383,7 +43386,7 @@
         <v>1</v>
       </c>
       <c r="I554" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J554" t="n">
         <v>11086</v>
@@ -43442,10 +43445,10 @@
         <v>300</v>
       </c>
       <c r="D555" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E555" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F555" t="s">
         <v>85</v>
@@ -43457,7 +43460,7 @@
         <v>1</v>
       </c>
       <c r="I555" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J555" t="n">
         <v>11086</v>
@@ -43478,7 +43481,7 @@
         <v>86</v>
       </c>
       <c r="P555" t="n">
-        <v>11014</v>
+        <v>11012</v>
       </c>
       <c r="Q555" t="n">
         <v>1</v>
@@ -43516,10 +43519,10 @@
         <v>301</v>
       </c>
       <c r="D556" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E556" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F556" t="s">
         <v>85</v>
@@ -43531,7 +43534,7 @@
         <v>1</v>
       </c>
       <c r="I556" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J556" t="n">
         <v>11086</v>
@@ -43590,10 +43593,10 @@
         <v>302</v>
       </c>
       <c r="D557" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E557" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F557" t="s">
         <v>85</v>
@@ -43605,7 +43608,7 @@
         <v>1</v>
       </c>
       <c r="I557" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J557" t="n">
         <v>11086</v>
@@ -43626,7 +43629,7 @@
         <v>86</v>
       </c>
       <c r="P557" t="n">
-        <v>11057</v>
+        <v>11055</v>
       </c>
       <c r="Q557" t="n">
         <v>1</v>
@@ -43664,10 +43667,10 @@
         <v>303</v>
       </c>
       <c r="D558" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E558" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F558" t="s">
         <v>85</v>
@@ -43679,7 +43682,7 @@
         <v>1</v>
       </c>
       <c r="I558" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J558" t="n">
         <v>11086</v>
@@ -43738,10 +43741,10 @@
         <v>304</v>
       </c>
       <c r="D559" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E559" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F559" t="s">
         <v>85</v>
@@ -43753,7 +43756,7 @@
         <v>1</v>
       </c>
       <c r="I559" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J559" t="n">
         <v>11086</v>
@@ -43812,10 +43815,10 @@
         <v>305</v>
       </c>
       <c r="D560" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E560" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F560" t="s">
         <v>85</v>
@@ -43827,7 +43830,7 @@
         <v>1</v>
       </c>
       <c r="I560" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J560" t="n">
         <v>11086</v>
@@ -43886,10 +43889,10 @@
         <v>306</v>
       </c>
       <c r="D561" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E561" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F561" t="s">
         <v>85</v>
@@ -43901,7 +43904,7 @@
         <v>1</v>
       </c>
       <c r="I561" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J561" t="n">
         <v>11086</v>
@@ -43960,10 +43963,10 @@
         <v>307</v>
       </c>
       <c r="D562" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E562" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F562" t="s">
         <v>85</v>
@@ -43975,7 +43978,7 @@
         <v>1</v>
       </c>
       <c r="I562" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J562" t="n">
         <v>11086</v>
@@ -43984,7 +43987,7 @@
         <v>1</v>
       </c>
       <c r="L562" t="n">
-        <v>5.4115454848073e-318</v>
+        <v>8.20148972096469e-322</v>
       </c>
       <c r="M562" t="n">
         <v>1</v>
@@ -43996,7 +43999,7 @@
         <v>86</v>
       </c>
       <c r="P562" t="n">
-        <v>11034</v>
+        <v>11033</v>
       </c>
       <c r="Q562" t="n">
         <v>1</v>
@@ -44034,10 +44037,10 @@
         <v>308</v>
       </c>
       <c r="D563" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E563" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F563" t="s">
         <v>85</v>
@@ -44049,7 +44052,7 @@
         <v>1</v>
       </c>
       <c r="I563" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J563" t="n">
         <v>11086</v>
@@ -44070,7 +44073,7 @@
         <v>86</v>
       </c>
       <c r="P563" t="n">
-        <v>11074</v>
+        <v>11073</v>
       </c>
       <c r="Q563" t="n">
         <v>1</v>
@@ -44108,10 +44111,10 @@
         <v>309</v>
       </c>
       <c r="D564" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E564" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F564" t="s">
         <v>85</v>
@@ -44123,7 +44126,7 @@
         <v>1</v>
       </c>
       <c r="I564" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J564" t="n">
         <v>11086</v>
@@ -44182,10 +44185,10 @@
         <v>310</v>
       </c>
       <c r="D565" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E565" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F565" t="s">
         <v>85</v>
@@ -44197,7 +44200,7 @@
         <v>1</v>
       </c>
       <c r="I565" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J565" t="n">
         <v>11086</v>
@@ -44256,10 +44259,10 @@
         <v>311</v>
       </c>
       <c r="D566" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E566" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F566" t="s">
         <v>85</v>
@@ -44271,7 +44274,7 @@
         <v>1</v>
       </c>
       <c r="I566" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J566" t="n">
         <v>11086</v>
@@ -44330,10 +44333,10 @@
         <v>312</v>
       </c>
       <c r="D567" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E567" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F567" t="s">
         <v>85</v>
@@ -44345,7 +44348,7 @@
         <v>1</v>
       </c>
       <c r="I567" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J567" t="n">
         <v>11086</v>
@@ -44354,7 +44357,7 @@
         <v>1</v>
       </c>
       <c r="L567" t="n">
-        <v>2.11644222574889e-297</v>
+        <v>5.86244347843845e-301</v>
       </c>
       <c r="M567" t="n">
         <v>1</v>
@@ -44404,10 +44407,10 @@
         <v>313</v>
       </c>
       <c r="D568" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E568" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F568" t="s">
         <v>85</v>
@@ -44419,7 +44422,7 @@
         <v>1</v>
       </c>
       <c r="I568" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J568" t="n">
         <v>11086</v>
@@ -44428,7 +44431,7 @@
         <v>1</v>
       </c>
       <c r="L568" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000218879158067762</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000231920126144681</v>
       </c>
       <c r="M568" t="n">
         <v>1</v>
@@ -44478,10 +44481,10 @@
         <v>314</v>
       </c>
       <c r="D569" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E569" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F569" t="s">
         <v>85</v>
@@ -44493,7 +44496,7 @@
         <v>1</v>
       </c>
       <c r="I569" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J569" t="n">
         <v>11086</v>
@@ -44502,7 +44505,7 @@
         <v>1</v>
       </c>
       <c r="L569" t="n">
-        <v>3.26685147446007e-210</v>
+        <v>1.0325967027683e-215</v>
       </c>
       <c r="M569" t="n">
         <v>1</v>
@@ -44552,10 +44555,10 @@
         <v>315</v>
       </c>
       <c r="D570" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E570" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F570" t="s">
         <v>85</v>
@@ -44567,7 +44570,7 @@
         <v>1</v>
       </c>
       <c r="I570" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J570" t="n">
         <v>11086</v>
@@ -44576,7 +44579,7 @@
         <v>1</v>
       </c>
       <c r="L570" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000617911851506528</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000239746501428675</v>
       </c>
       <c r="M570" t="n">
         <v>1</v>
@@ -44626,10 +44629,10 @@
         <v>316</v>
       </c>
       <c r="D571" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E571" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F571" t="s">
         <v>85</v>
@@ -44641,7 +44644,7 @@
         <v>1</v>
       </c>
       <c r="I571" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J571" t="n">
         <v>11086</v>
@@ -44650,7 +44653,7 @@
         <v>1</v>
       </c>
       <c r="L571" t="n">
-        <v>2.93528880089549e-211</v>
+        <v>3.1836377406411e-218</v>
       </c>
       <c r="M571" t="n">
         <v>1</v>
@@ -44700,10 +44703,10 @@
         <v>327</v>
       </c>
       <c r="D572" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E572" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F572" t="s">
         <v>85</v>
@@ -44715,7 +44718,7 @@
         <v>0</v>
       </c>
       <c r="I572" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J572" t="n">
         <v>11086</v>
@@ -44724,7 +44727,7 @@
         <v>1</v>
       </c>
       <c r="L572" t="n">
-        <v>0.00000000000000000000000000000000000000456873664082092</v>
+        <v>0.000000000000000000000000000000000000000000000130870824982016</v>
       </c>
       <c r="M572" t="n">
         <v>1</v>
@@ -44774,10 +44777,10 @@
         <v>328</v>
       </c>
       <c r="D573" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E573" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F573" t="s">
         <v>85</v>
@@ -44789,7 +44792,7 @@
         <v>0</v>
       </c>
       <c r="I573" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J573" t="n">
         <v>11086</v>
@@ -44798,7 +44801,7 @@
         <v>1</v>
       </c>
       <c r="L573" t="n">
-        <v>0.0000000000000000000000000000000000000000000038910634886186</v>
+        <v>0.00000000000000000000000000000000000000000000000000204962503281682</v>
       </c>
       <c r="M573" t="n">
         <v>1</v>
@@ -44848,10 +44851,10 @@
         <v>329</v>
       </c>
       <c r="D574" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E574" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F574" t="s">
         <v>85</v>
@@ -44863,7 +44866,7 @@
         <v>0</v>
       </c>
       <c r="I574" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J574" t="n">
         <v>11086</v>
@@ -44872,7 +44875,7 @@
         <v>1</v>
       </c>
       <c r="L574" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000258570010508563</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000901186367397149</v>
       </c>
       <c r="M574" t="n">
         <v>1</v>
@@ -44922,22 +44925,22 @@
         <v>330</v>
       </c>
       <c r="D575" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E575" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F575" t="s">
-        <v>85</v>
+        <v>403</v>
       </c>
       <c r="G575" t="s">
-        <v>86</v>
+        <v>410</v>
       </c>
       <c r="H575" t="b">
         <v>0</v>
       </c>
       <c r="I575" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J575" t="n">
         <v>11086</v>
@@ -44946,7 +44949,7 @@
         <v>1</v>
       </c>
       <c r="L575" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000698047415941387</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000632469082528837</v>
       </c>
       <c r="M575" t="n">
         <v>1</v>
@@ -44958,10 +44961,10 @@
         <v>86</v>
       </c>
       <c r="P575" t="n">
-        <v>11058</v>
+        <v>11057</v>
       </c>
       <c r="Q575" t="n">
-        <v>1</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="R575" t="n">
         <v>1</v>
@@ -44970,7 +44973,7 @@
         <v>0.5</v>
       </c>
       <c r="T575" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="U575" t="n">
         <v>16</v>
@@ -44996,10 +44999,10 @@
         <v>331</v>
       </c>
       <c r="D576" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E576" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F576" t="s">
         <v>85</v>
@@ -45011,7 +45014,7 @@
         <v>0</v>
       </c>
       <c r="I576" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J576" t="n">
         <v>11086</v>
@@ -45020,7 +45023,7 @@
         <v>1</v>
       </c>
       <c r="L576" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000157862717295742</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000303303434784559</v>
       </c>
       <c r="M576" t="n">
         <v>1</v>
@@ -45032,7 +45035,7 @@
         <v>86</v>
       </c>
       <c r="P576" t="n">
-        <v>11041</v>
+        <v>11039</v>
       </c>
       <c r="Q576" t="n">
         <v>1</v>
@@ -45070,10 +45073,10 @@
         <v>332</v>
       </c>
       <c r="D577" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E577" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F577" t="s">
         <v>85</v>
@@ -45085,7 +45088,7 @@
         <v>1</v>
       </c>
       <c r="I577" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J577" t="n">
         <v>11086</v>
@@ -45094,7 +45097,7 @@
         <v>1</v>
       </c>
       <c r="L577" t="n">
-        <v>0.00000000000000000000000000000000000356876004746322</v>
+        <v>0.00000000000000000000000000000000000000118516962873187</v>
       </c>
       <c r="M577" t="n">
         <v>1</v>
@@ -45144,10 +45147,10 @@
         <v>333</v>
       </c>
       <c r="D578" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E578" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F578" t="s">
         <v>85</v>
@@ -45159,7 +45162,7 @@
         <v>1</v>
       </c>
       <c r="I578" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J578" t="n">
         <v>11086</v>
@@ -45168,7 +45171,7 @@
         <v>1</v>
       </c>
       <c r="L578" t="n">
-        <v>0.0000000000000000000000104677727033123</v>
+        <v>0.0000000000000000000000000000437048964007497</v>
       </c>
       <c r="M578" t="n">
         <v>1</v>
@@ -45218,10 +45221,10 @@
         <v>334</v>
       </c>
       <c r="D579" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E579" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F579" t="s">
         <v>85</v>
@@ -45233,7 +45236,7 @@
         <v>1</v>
       </c>
       <c r="I579" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J579" t="n">
         <v>11086</v>
@@ -45242,7 +45245,7 @@
         <v>1</v>
       </c>
       <c r="L579" t="n">
-        <v>0.000000000000000000000000000000013420936909423</v>
+        <v>0.000000000000000000000000000000000000000000920902094605259</v>
       </c>
       <c r="M579" t="n">
         <v>1</v>
@@ -45254,7 +45257,7 @@
         <v>86</v>
       </c>
       <c r="P579" t="n">
-        <v>11070</v>
+        <v>11069</v>
       </c>
       <c r="Q579" t="n">
         <v>1</v>
@@ -45292,10 +45295,10 @@
         <v>335</v>
       </c>
       <c r="D580" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E580" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F580" t="s">
         <v>85</v>
@@ -45307,19 +45310,19 @@
         <v>1</v>
       </c>
       <c r="I580" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J580" t="n">
         <v>11086</v>
       </c>
       <c r="K580" t="n">
-        <v>0.999999999986555</v>
+        <v>1</v>
       </c>
       <c r="L580" t="n">
-        <v>0.0000000000134455429393434</v>
+        <v>0.000000000000000326609461106699</v>
       </c>
       <c r="M580" t="n">
-        <v>0.999999999973109</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="N580" t="s">
         <v>85</v>
@@ -45366,34 +45369,34 @@
         <v>336</v>
       </c>
       <c r="D581" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E581" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F581" t="s">
-        <v>403</v>
+        <v>85</v>
       </c>
       <c r="G581" t="s">
-        <v>410</v>
+        <v>86</v>
       </c>
       <c r="H581" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I581" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J581" t="n">
         <v>11086</v>
       </c>
       <c r="K581" t="n">
-        <v>0.998931288378518</v>
+        <v>0.999903933948035</v>
       </c>
       <c r="L581" t="n">
-        <v>0.00106871162148165</v>
+        <v>0.000096066051964831</v>
       </c>
       <c r="M581" t="n">
-        <v>0.997862576757037</v>
+        <v>0.99980786789607</v>
       </c>
       <c r="N581" t="s">
         <v>85</v>
@@ -45402,19 +45405,19 @@
         <v>86</v>
       </c>
       <c r="P581" t="n">
-        <v>11077</v>
+        <v>11076</v>
       </c>
       <c r="Q581" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R581" t="n">
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="S581" t="n">
         <v>0.5</v>
       </c>
       <c r="T581" t="n">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="U581" t="n">
         <v>16</v>
@@ -45440,10 +45443,10 @@
         <v>337</v>
       </c>
       <c r="D582" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E582" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F582" t="s">
         <v>85</v>
@@ -45455,7 +45458,7 @@
         <v>1</v>
       </c>
       <c r="I582" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J582" t="n">
         <v>11086</v>
@@ -45476,7 +45479,7 @@
         <v>86</v>
       </c>
       <c r="P582" t="n">
-        <v>11052</v>
+        <v>11051</v>
       </c>
       <c r="Q582" t="n">
         <v>1</v>
@@ -45514,10 +45517,10 @@
         <v>338</v>
       </c>
       <c r="D583" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E583" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F583" t="s">
         <v>85</v>
@@ -45529,7 +45532,7 @@
         <v>1</v>
       </c>
       <c r="I583" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J583" t="n">
         <v>11086</v>
@@ -45550,7 +45553,7 @@
         <v>86</v>
       </c>
       <c r="P583" t="n">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="Q583" t="n">
         <v>1</v>
@@ -45588,10 +45591,10 @@
         <v>339</v>
       </c>
       <c r="D584" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E584" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F584" t="s">
         <v>85</v>
@@ -45603,7 +45606,7 @@
         <v>1</v>
       </c>
       <c r="I584" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J584" t="n">
         <v>11086</v>
@@ -45662,10 +45665,10 @@
         <v>340</v>
       </c>
       <c r="D585" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E585" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F585" t="s">
         <v>85</v>
@@ -45677,7 +45680,7 @@
         <v>1</v>
       </c>
       <c r="I585" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J585" t="n">
         <v>11086</v>
@@ -45698,7 +45701,7 @@
         <v>86</v>
       </c>
       <c r="P585" t="n">
-        <v>10978</v>
+        <v>10980</v>
       </c>
       <c r="Q585" t="n">
         <v>1</v>
@@ -45736,10 +45739,10 @@
         <v>341</v>
       </c>
       <c r="D586" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E586" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F586" t="s">
         <v>85</v>
@@ -45751,7 +45754,7 @@
         <v>1</v>
       </c>
       <c r="I586" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J586" t="n">
         <v>11086</v>
@@ -45772,7 +45775,7 @@
         <v>86</v>
       </c>
       <c r="P586" t="n">
-        <v>10263</v>
+        <v>10265</v>
       </c>
       <c r="Q586" t="n">
         <v>1</v>
@@ -45810,10 +45813,10 @@
         <v>342</v>
       </c>
       <c r="D587" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E587" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F587" t="s">
         <v>85</v>
@@ -45825,7 +45828,7 @@
         <v>1</v>
       </c>
       <c r="I587" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J587" t="n">
         <v>11086</v>
@@ -45846,7 +45849,7 @@
         <v>86</v>
       </c>
       <c r="P587" t="n">
-        <v>11063</v>
+        <v>11062</v>
       </c>
       <c r="Q587" t="n">
         <v>1</v>
@@ -45884,10 +45887,10 @@
         <v>343</v>
       </c>
       <c r="D588" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E588" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F588" t="s">
         <v>85</v>
@@ -45899,7 +45902,7 @@
         <v>1</v>
       </c>
       <c r="I588" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J588" t="n">
         <v>11086</v>
@@ -45958,10 +45961,10 @@
         <v>344</v>
       </c>
       <c r="D589" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E589" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F589" t="s">
         <v>85</v>
@@ -45973,7 +45976,7 @@
         <v>1</v>
       </c>
       <c r="I589" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J589" t="n">
         <v>11086</v>
@@ -45994,7 +45997,7 @@
         <v>86</v>
       </c>
       <c r="P589" t="n">
-        <v>11056</v>
+        <v>11057</v>
       </c>
       <c r="Q589" t="n">
         <v>1</v>
@@ -46032,10 +46035,10 @@
         <v>345</v>
       </c>
       <c r="D590" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E590" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F590" t="s">
         <v>85</v>
@@ -46047,7 +46050,7 @@
         <v>1</v>
       </c>
       <c r="I590" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J590" t="n">
         <v>11086</v>
@@ -46106,10 +46109,10 @@
         <v>346</v>
       </c>
       <c r="D591" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E591" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F591" t="s">
         <v>85</v>
@@ -46121,7 +46124,7 @@
         <v>1</v>
       </c>
       <c r="I591" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J591" t="n">
         <v>11086</v>
@@ -46142,7 +46145,7 @@
         <v>86</v>
       </c>
       <c r="P591" t="n">
-        <v>11067</v>
+        <v>11068</v>
       </c>
       <c r="Q591" t="n">
         <v>1</v>
@@ -46180,10 +46183,10 @@
         <v>352</v>
       </c>
       <c r="D592" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E592" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F592" t="s">
         <v>403</v>
@@ -46195,7 +46198,7 @@
         <v>0</v>
       </c>
       <c r="I592" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J592" t="n">
         <v>11086</v>
@@ -46204,7 +46207,7 @@
         <v>1</v>
       </c>
       <c r="L592" t="n">
-        <v>0.00000000000000000000000000083296070494044</v>
+        <v>0.000000000000000000000000000000000430464598208738</v>
       </c>
       <c r="M592" t="n">
         <v>1</v>
@@ -46254,10 +46257,10 @@
         <v>353</v>
       </c>
       <c r="D593" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E593" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F593" t="s">
         <v>403</v>
@@ -46269,7 +46272,7 @@
         <v>0</v>
       </c>
       <c r="I593" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J593" t="n">
         <v>11086</v>
@@ -46278,7 +46281,7 @@
         <v>1</v>
       </c>
       <c r="L593" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000558060772277123</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000303576638172574</v>
       </c>
       <c r="M593" t="n">
         <v>1</v>
@@ -46290,7 +46293,7 @@
         <v>86</v>
       </c>
       <c r="P593" t="n">
-        <v>11071</v>
+        <v>11070</v>
       </c>
       <c r="Q593" t="n">
         <v>0.666666666666667</v>
@@ -46328,10 +46331,10 @@
         <v>354</v>
       </c>
       <c r="D594" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E594" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F594" t="s">
         <v>403</v>
@@ -46343,7 +46346,7 @@
         <v>0</v>
       </c>
       <c r="I594" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J594" t="n">
         <v>11086</v>
@@ -46352,7 +46355,7 @@
         <v>1</v>
       </c>
       <c r="L594" t="n">
-        <v>0.00000000000000000260685212810809</v>
+        <v>0.000000000000000110930987525257</v>
       </c>
       <c r="M594" t="n">
         <v>1</v>
@@ -46402,10 +46405,10 @@
         <v>355</v>
       </c>
       <c r="D595" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E595" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F595" t="s">
         <v>403</v>
@@ -46417,19 +46420,19 @@
         <v>0</v>
       </c>
       <c r="I595" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J595" t="n">
         <v>11086</v>
       </c>
       <c r="K595" t="n">
-        <v>0.999999873859361</v>
+        <v>0.969066387534419</v>
       </c>
       <c r="L595" t="n">
-        <v>0.000000126140639293593</v>
+        <v>0.0309336124655812</v>
       </c>
       <c r="M595" t="n">
-        <v>0.999999747718721</v>
+        <v>0.938132775068838</v>
       </c>
       <c r="N595" t="s">
         <v>85</v>
@@ -46438,13 +46441,13 @@
         <v>86</v>
       </c>
       <c r="P595" t="n">
-        <v>11064</v>
+        <v>11063</v>
       </c>
       <c r="Q595" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="R595" t="n">
         <v>0.333333333333333</v>
-      </c>
-      <c r="R595" t="n">
-        <v>0.666666666666667</v>
       </c>
       <c r="S595" t="n">
         <v>0.5</v>
@@ -46476,55 +46479,55 @@
         <v>356</v>
       </c>
       <c r="D596" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E596" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F596" t="s">
         <v>403</v>
       </c>
       <c r="G596" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="H596" t="b">
         <v>0</v>
       </c>
       <c r="I596" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J596" t="n">
         <v>11086</v>
       </c>
       <c r="K596" t="n">
-        <v>0.6300753177649</v>
+        <v>0.999999999705907</v>
       </c>
       <c r="L596" t="n">
-        <v>0.3699246822351</v>
+        <v>0.000000000294092962775289</v>
       </c>
       <c r="M596" t="n">
-        <v>0.260150635529801</v>
+        <v>0.999999999411814</v>
       </c>
       <c r="N596" t="s">
-        <v>418</v>
+        <v>85</v>
       </c>
       <c r="O596" t="s">
         <v>86</v>
       </c>
       <c r="P596" t="n">
-        <v>10971</v>
+        <v>10965</v>
       </c>
       <c r="Q596" t="n">
-        <v>0.166666666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="R596" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S596" t="n">
         <v>0.5</v>
       </c>
       <c r="T596" t="n">
-        <v>11086</v>
+        <v>2000</v>
       </c>
       <c r="U596" t="n">
         <v>16</v>
@@ -46550,10 +46553,10 @@
         <v>357</v>
       </c>
       <c r="D597" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E597" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F597" t="s">
         <v>85</v>
@@ -46565,7 +46568,7 @@
         <v>1</v>
       </c>
       <c r="I597" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J597" t="n">
         <v>11086</v>
@@ -46574,7 +46577,7 @@
         <v>1</v>
       </c>
       <c r="L597" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000443639879686162</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000135838006612019</v>
       </c>
       <c r="M597" t="n">
         <v>1</v>
@@ -46624,10 +46627,10 @@
         <v>358</v>
       </c>
       <c r="D598" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E598" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F598" t="s">
         <v>403</v>
@@ -46639,7 +46642,7 @@
         <v>1</v>
       </c>
       <c r="I598" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J598" t="n">
         <v>11086</v>
@@ -46648,7 +46651,7 @@
         <v>1</v>
       </c>
       <c r="L598" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000109832414624354</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000108361250059879</v>
       </c>
       <c r="M598" t="n">
         <v>1</v>
@@ -46698,10 +46701,10 @@
         <v>359</v>
       </c>
       <c r="D599" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E599" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F599" t="s">
         <v>85</v>
@@ -46713,7 +46716,7 @@
         <v>1</v>
       </c>
       <c r="I599" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J599" t="n">
         <v>11086</v>
@@ -46722,7 +46725,7 @@
         <v>1</v>
       </c>
       <c r="L599" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000006555190934325</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000277261375332735</v>
       </c>
       <c r="M599" t="n">
         <v>1</v>
@@ -46734,7 +46737,7 @@
         <v>86</v>
       </c>
       <c r="P599" t="n">
-        <v>11074</v>
+        <v>11073</v>
       </c>
       <c r="Q599" t="n">
         <v>1</v>
@@ -46772,10 +46775,10 @@
         <v>360</v>
       </c>
       <c r="D600" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E600" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F600" t="s">
         <v>85</v>
@@ -46787,7 +46790,7 @@
         <v>1</v>
       </c>
       <c r="I600" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J600" t="n">
         <v>11086</v>
@@ -46796,7 +46799,7 @@
         <v>1</v>
       </c>
       <c r="L600" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183427835174082</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000596699740940095</v>
       </c>
       <c r="M600" t="n">
         <v>1</v>
@@ -46846,10 +46849,10 @@
         <v>361</v>
       </c>
       <c r="D601" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E601" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F601" t="s">
         <v>85</v>
@@ -46861,7 +46864,7 @@
         <v>1</v>
       </c>
       <c r="I601" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J601" t="n">
         <v>11086</v>
@@ -46870,7 +46873,7 @@
         <v>1</v>
       </c>
       <c r="L601" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000532525427963025</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000246538901696513</v>
       </c>
       <c r="M601" t="n">
         <v>1</v>
@@ -46920,10 +46923,10 @@
         <v>362</v>
       </c>
       <c r="D602" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E602" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F602" t="s">
         <v>85</v>
@@ -46935,7 +46938,7 @@
         <v>1</v>
       </c>
       <c r="I602" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J602" t="n">
         <v>11086</v>
@@ -46956,7 +46959,7 @@
         <v>86</v>
       </c>
       <c r="P602" t="n">
-        <v>10801</v>
+        <v>10797</v>
       </c>
       <c r="Q602" t="n">
         <v>1</v>
@@ -46994,10 +46997,10 @@
         <v>363</v>
       </c>
       <c r="D603" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E603" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F603" t="s">
         <v>85</v>
@@ -47009,7 +47012,7 @@
         <v>1</v>
       </c>
       <c r="I603" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J603" t="n">
         <v>11086</v>
@@ -47030,7 +47033,7 @@
         <v>86</v>
       </c>
       <c r="P603" t="n">
-        <v>10812</v>
+        <v>10814</v>
       </c>
       <c r="Q603" t="n">
         <v>1</v>
@@ -47068,10 +47071,10 @@
         <v>364</v>
       </c>
       <c r="D604" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E604" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F604" t="s">
         <v>85</v>
@@ -47083,7 +47086,7 @@
         <v>1</v>
       </c>
       <c r="I604" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J604" t="n">
         <v>11086</v>
@@ -47104,7 +47107,7 @@
         <v>86</v>
       </c>
       <c r="P604" t="n">
-        <v>10674</v>
+        <v>10671</v>
       </c>
       <c r="Q604" t="n">
         <v>1</v>
@@ -47142,10 +47145,10 @@
         <v>365</v>
       </c>
       <c r="D605" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E605" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F605" t="s">
         <v>403</v>
@@ -47157,7 +47160,7 @@
         <v>1</v>
       </c>
       <c r="I605" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J605" t="n">
         <v>11086</v>
@@ -47166,7 +47169,7 @@
         <v>1</v>
       </c>
       <c r="L605" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000961878786821219</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000169349341832513</v>
       </c>
       <c r="M605" t="n">
         <v>1</v>
@@ -47216,10 +47219,10 @@
         <v>366</v>
       </c>
       <c r="D606" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E606" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F606" t="s">
         <v>85</v>
@@ -47231,7 +47234,7 @@
         <v>1</v>
       </c>
       <c r="I606" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J606" t="n">
         <v>11086</v>
@@ -47252,7 +47255,7 @@
         <v>86</v>
       </c>
       <c r="P606" t="n">
-        <v>10821</v>
+        <v>10823</v>
       </c>
       <c r="Q606" t="n">
         <v>1</v>
@@ -47290,10 +47293,10 @@
         <v>372</v>
       </c>
       <c r="D607" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E607" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F607" t="s">
         <v>85</v>
@@ -47305,7 +47308,7 @@
         <v>1</v>
       </c>
       <c r="I607" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J607" t="n">
         <v>11086</v>
@@ -47326,7 +47329,7 @@
         <v>86</v>
       </c>
       <c r="P607" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
       <c r="Q607" t="n">
         <v>1</v>
@@ -47364,10 +47367,10 @@
         <v>373</v>
       </c>
       <c r="D608" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E608" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F608" t="s">
         <v>85</v>
@@ -47379,7 +47382,7 @@
         <v>1</v>
       </c>
       <c r="I608" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J608" t="n">
         <v>11086</v>
@@ -47400,7 +47403,7 @@
         <v>86</v>
       </c>
       <c r="P608" t="n">
-        <v>11061</v>
+        <v>11060</v>
       </c>
       <c r="Q608" t="n">
         <v>1</v>
@@ -47438,10 +47441,10 @@
         <v>374</v>
       </c>
       <c r="D609" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E609" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F609" t="s">
         <v>85</v>
@@ -47453,7 +47456,7 @@
         <v>1</v>
       </c>
       <c r="I609" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J609" t="n">
         <v>11086</v>
@@ -47474,7 +47477,7 @@
         <v>86</v>
       </c>
       <c r="P609" t="n">
-        <v>11078</v>
+        <v>11077</v>
       </c>
       <c r="Q609" t="n">
         <v>1</v>
@@ -47512,10 +47515,10 @@
         <v>375</v>
       </c>
       <c r="D610" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E610" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F610" t="s">
         <v>85</v>
@@ -47527,7 +47530,7 @@
         <v>1</v>
       </c>
       <c r="I610" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J610" t="n">
         <v>11086</v>
@@ -47548,7 +47551,7 @@
         <v>86</v>
       </c>
       <c r="P610" t="n">
-        <v>11083</v>
+        <v>11081</v>
       </c>
       <c r="Q610" t="n">
         <v>1</v>
@@ -47586,10 +47589,10 @@
         <v>376</v>
       </c>
       <c r="D611" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E611" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F611" t="s">
         <v>85</v>
@@ -47601,7 +47604,7 @@
         <v>1</v>
       </c>
       <c r="I611" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J611" t="n">
         <v>11086</v>
@@ -47660,10 +47663,10 @@
         <v>377</v>
       </c>
       <c r="D612" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E612" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F612" t="s">
         <v>85</v>
@@ -47675,7 +47678,7 @@
         <v>1</v>
       </c>
       <c r="I612" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J612" t="n">
         <v>11086</v>
@@ -47734,10 +47737,10 @@
         <v>378</v>
       </c>
       <c r="D613" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E613" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F613" t="s">
         <v>85</v>
@@ -47749,7 +47752,7 @@
         <v>1</v>
       </c>
       <c r="I613" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J613" t="n">
         <v>11086</v>
@@ -47808,10 +47811,10 @@
         <v>379</v>
       </c>
       <c r="D614" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E614" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F614" t="s">
         <v>85</v>
@@ -47823,7 +47826,7 @@
         <v>1</v>
       </c>
       <c r="I614" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J614" t="n">
         <v>11086</v>
@@ -47844,7 +47847,7 @@
         <v>86</v>
       </c>
       <c r="P614" t="n">
-        <v>11057</v>
+        <v>11056</v>
       </c>
       <c r="Q614" t="n">
         <v>1</v>
@@ -47882,10 +47885,10 @@
         <v>380</v>
       </c>
       <c r="D615" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E615" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F615" t="s">
         <v>85</v>
@@ -47897,7 +47900,7 @@
         <v>1</v>
       </c>
       <c r="I615" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J615" t="n">
         <v>11086</v>
@@ -47956,10 +47959,10 @@
         <v>381</v>
       </c>
       <c r="D616" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E616" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F616" t="s">
         <v>85</v>
@@ -47971,7 +47974,7 @@
         <v>1</v>
       </c>
       <c r="I616" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J616" t="n">
         <v>11086</v>
@@ -48030,10 +48033,10 @@
         <v>382</v>
       </c>
       <c r="D617" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E617" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F617" t="s">
         <v>85</v>
@@ -48045,7 +48048,7 @@
         <v>1</v>
       </c>
       <c r="I617" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J617" t="n">
         <v>11086</v>
@@ -48066,7 +48069,7 @@
         <v>86</v>
       </c>
       <c r="P617" t="n">
-        <v>11077</v>
+        <v>11075</v>
       </c>
       <c r="Q617" t="n">
         <v>1</v>
@@ -48104,10 +48107,10 @@
         <v>383</v>
       </c>
       <c r="D618" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E618" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F618" t="s">
         <v>85</v>
@@ -48119,7 +48122,7 @@
         <v>1</v>
       </c>
       <c r="I618" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J618" t="n">
         <v>11086</v>
@@ -48178,10 +48181,10 @@
         <v>384</v>
       </c>
       <c r="D619" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E619" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F619" t="s">
         <v>85</v>
@@ -48193,7 +48196,7 @@
         <v>1</v>
       </c>
       <c r="I619" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J619" t="n">
         <v>11086</v>
@@ -48214,7 +48217,7 @@
         <v>86</v>
       </c>
       <c r="P619" t="n">
-        <v>11075</v>
+        <v>11074</v>
       </c>
       <c r="Q619" t="n">
         <v>1</v>
@@ -48252,10 +48255,10 @@
         <v>385</v>
       </c>
       <c r="D620" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E620" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F620" t="s">
         <v>85</v>
@@ -48267,7 +48270,7 @@
         <v>1</v>
       </c>
       <c r="I620" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J620" t="n">
         <v>11086</v>
@@ -48288,7 +48291,7 @@
         <v>86</v>
       </c>
       <c r="P620" t="n">
-        <v>11073</v>
+        <v>11074</v>
       </c>
       <c r="Q620" t="n">
         <v>1</v>
@@ -48326,10 +48329,10 @@
         <v>386</v>
       </c>
       <c r="D621" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E621" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F621" t="s">
         <v>85</v>
@@ -48341,7 +48344,7 @@
         <v>1</v>
       </c>
       <c r="I621" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J621" t="n">
         <v>11086</v>
@@ -48400,10 +48403,10 @@
         <v>387</v>
       </c>
       <c r="D622" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E622" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F622" t="s">
         <v>85</v>
@@ -48415,7 +48418,7 @@
         <v>1</v>
       </c>
       <c r="I622" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J622" t="n">
         <v>11086</v>
@@ -48474,10 +48477,10 @@
         <v>388</v>
       </c>
       <c r="D623" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E623" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F623" t="s">
         <v>85</v>
@@ -48489,7 +48492,7 @@
         <v>1</v>
       </c>
       <c r="I623" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J623" t="n">
         <v>11086</v>
@@ -48548,10 +48551,10 @@
         <v>389</v>
       </c>
       <c r="D624" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E624" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F624" t="s">
         <v>85</v>
@@ -48563,7 +48566,7 @@
         <v>1</v>
       </c>
       <c r="I624" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J624" t="n">
         <v>11086</v>
@@ -48622,10 +48625,10 @@
         <v>390</v>
       </c>
       <c r="D625" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E625" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F625" t="s">
         <v>85</v>
@@ -48637,7 +48640,7 @@
         <v>1</v>
       </c>
       <c r="I625" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J625" t="n">
         <v>11086</v>
@@ -48696,10 +48699,10 @@
         <v>391</v>
       </c>
       <c r="D626" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E626" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F626" t="s">
         <v>85</v>
@@ -48711,7 +48714,7 @@
         <v>1</v>
       </c>
       <c r="I626" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J626" t="n">
         <v>11086</v>
@@ -48770,10 +48773,10 @@
         <v>392</v>
       </c>
       <c r="D627" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E627" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F627" t="s">
         <v>85</v>
@@ -48785,7 +48788,7 @@
         <v>1</v>
       </c>
       <c r="I627" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J627" t="n">
         <v>11086</v>
@@ -48844,10 +48847,10 @@
         <v>393</v>
       </c>
       <c r="D628" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E628" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F628" t="s">
         <v>85</v>
@@ -48859,7 +48862,7 @@
         <v>1</v>
       </c>
       <c r="I628" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J628" t="n">
         <v>11086</v>
@@ -48918,10 +48921,10 @@
         <v>394</v>
       </c>
       <c r="D629" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E629" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F629" t="s">
         <v>85</v>
@@ -48933,7 +48936,7 @@
         <v>1</v>
       </c>
       <c r="I629" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J629" t="n">
         <v>11086</v>
@@ -48992,10 +48995,10 @@
         <v>395</v>
       </c>
       <c r="D630" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E630" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F630" t="s">
         <v>85</v>
@@ -49007,7 +49010,7 @@
         <v>1</v>
       </c>
       <c r="I630" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J630" t="n">
         <v>11086</v>
@@ -49066,10 +49069,10 @@
         <v>396</v>
       </c>
       <c r="D631" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E631" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F631" t="s">
         <v>85</v>
@@ -49081,7 +49084,7 @@
         <v>1</v>
       </c>
       <c r="I631" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J631" t="n">
         <v>11086</v>
@@ -49140,10 +49143,10 @@
         <v>397</v>
       </c>
       <c r="D632" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E632" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F632" t="s">
         <v>85</v>
@@ -49155,7 +49158,7 @@
         <v>1</v>
       </c>
       <c r="I632" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J632" t="n">
         <v>11086</v>
@@ -49176,7 +49179,7 @@
         <v>86</v>
       </c>
       <c r="P632" t="n">
-        <v>11062</v>
+        <v>11061</v>
       </c>
       <c r="Q632" t="n">
         <v>1</v>
@@ -49214,10 +49217,10 @@
         <v>398</v>
       </c>
       <c r="D633" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E633" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F633" t="s">
         <v>85</v>
@@ -49229,7 +49232,7 @@
         <v>1</v>
       </c>
       <c r="I633" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J633" t="n">
         <v>11086</v>
@@ -49250,7 +49253,7 @@
         <v>86</v>
       </c>
       <c r="P633" t="n">
-        <v>11067</v>
+        <v>11068</v>
       </c>
       <c r="Q633" t="n">
         <v>1</v>
@@ -49288,10 +49291,10 @@
         <v>399</v>
       </c>
       <c r="D634" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E634" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F634" t="s">
         <v>85</v>
@@ -49303,7 +49306,7 @@
         <v>1</v>
       </c>
       <c r="I634" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J634" t="n">
         <v>11086</v>
@@ -49362,10 +49365,10 @@
         <v>400</v>
       </c>
       <c r="D635" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E635" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F635" t="s">
         <v>85</v>
@@ -49377,7 +49380,7 @@
         <v>1</v>
       </c>
       <c r="I635" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J635" t="n">
         <v>11086</v>
@@ -49436,10 +49439,10 @@
         <v>401</v>
       </c>
       <c r="D636" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E636" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F636" t="s">
         <v>85</v>
@@ -49451,7 +49454,7 @@
         <v>1</v>
       </c>
       <c r="I636" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J636" t="n">
         <v>11086</v>
@@ -49510,10 +49513,10 @@
         <v>402</v>
       </c>
       <c r="D637" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E637" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F637" t="s">
         <v>403</v>
@@ -49525,7 +49528,7 @@
         <v>1</v>
       </c>
       <c r="I637" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J637" t="n">
         <v>11086</v>
@@ -49534,7 +49537,7 @@
         <v>1</v>
       </c>
       <c r="L637" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000118172881021672</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000329239837282298</v>
       </c>
       <c r="M637" t="n">
         <v>1</v>
@@ -49546,7 +49549,7 @@
         <v>86</v>
       </c>
       <c r="P637" t="n">
-        <v>2324</v>
+        <v>2318</v>
       </c>
       <c r="Q637" t="n">
         <v>1</v>
@@ -49584,10 +49587,10 @@
         <v>405</v>
       </c>
       <c r="D638" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E638" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F638" t="s">
         <v>85</v>
@@ -49599,7 +49602,7 @@
         <v>1</v>
       </c>
       <c r="I638" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J638" t="n">
         <v>11086</v>
@@ -49620,7 +49623,7 @@
         <v>86</v>
       </c>
       <c r="P638" t="n">
-        <v>11074</v>
+        <v>11073</v>
       </c>
       <c r="Q638" t="n">
         <v>1</v>
@@ -49658,10 +49661,10 @@
         <v>406</v>
       </c>
       <c r="D639" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E639" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F639" t="s">
         <v>85</v>
@@ -49673,7 +49676,7 @@
         <v>1</v>
       </c>
       <c r="I639" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J639" t="n">
         <v>11086</v>
@@ -49732,10 +49735,10 @@
         <v>407</v>
       </c>
       <c r="D640" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E640" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F640" t="s">
         <v>403</v>
@@ -49747,7 +49750,7 @@
         <v>1</v>
       </c>
       <c r="I640" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J640" t="n">
         <v>11086</v>
@@ -49756,7 +49759,7 @@
         <v>1</v>
       </c>
       <c r="L640" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147848698547005</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000034547059855892</v>
       </c>
       <c r="M640" t="n">
         <v>1</v>
@@ -49768,7 +49771,7 @@
         <v>86</v>
       </c>
       <c r="P640" t="n">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="Q640" t="n">
         <v>1</v>
@@ -49806,10 +49809,10 @@
         <v>408</v>
       </c>
       <c r="D641" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E641" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F641" t="s">
         <v>85</v>
@@ -49821,7 +49824,7 @@
         <v>1</v>
       </c>
       <c r="I641" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J641" t="n">
         <v>11086</v>
@@ -50013,19 +50016,19 @@
         <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>0.955223880597015</v>
+        <v>0.970149253731343</v>
       </c>
       <c r="G5" t="n">
-        <v>0.955223880597015</v>
+        <v>0.970149253731343</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91044776119403</v>
+        <v>0.895522388059702</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0895522388059701</v>
+        <v>0.104477611940299</v>
       </c>
     </row>
     <row r="6">
@@ -50033,7 +50036,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
@@ -50080,10 +50083,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91304347826087</v>
+        <v>0.869565217391304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.130434782608696</v>
       </c>
     </row>
     <row r="8">
@@ -50091,7 +50094,7 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C8" t="n">
         <v>80</v>
@@ -50120,7 +50123,7 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C9" t="n">
         <v>90</v>
@@ -50129,13 +50132,13 @@
         <v>90</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>0.811111111111111</v>
+        <v>0.822222222222222</v>
       </c>
       <c r="G9" t="n">
-        <v>0.811111111111111</v>
+        <v>0.822222222222222</v>
       </c>
       <c r="H9" t="n">
         <v>0.855555555555556</v>
@@ -50149,7 +50152,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C10" t="n">
         <v>45</v>
@@ -50198,10 +50201,10 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
@@ -50249,10 +50252,10 @@
         <v>409</v>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>0.955223880597015</v>
+        <v>0.970149253731343</v>
       </c>
     </row>
     <row r="5">
@@ -50300,10 +50303,10 @@
         <v>412</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0447761194029851</v>
+        <v>0.0298507462686567</v>
       </c>
     </row>
     <row r="8">
@@ -50311,10 +50314,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -50328,16 +50331,16 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>0.811111111111111</v>
+        <v>0.822222222222222</v>
       </c>
     </row>
     <row r="10">
@@ -50345,10 +50348,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D10" t="n">
         <v>45</v>
@@ -50362,10 +50365,10 @@
         <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D11" t="n">
         <v>80</v>
@@ -50379,16 +50382,16 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0555555555555556</v>
       </c>
     </row>
     <row r="13">
@@ -50396,10 +50399,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C13" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
@@ -50430,7 +50433,7 @@
         <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
@@ -50463,7 +50466,7 @@
         <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
@@ -50474,18 +50477,18 @@
         <v>410</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>413</v>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -50493,10 +50496,10 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>410</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -50504,10 +50507,10 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -50515,10 +50518,10 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -50543,7 +50546,7 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
@@ -51090,178 +51093,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B15" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B16" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>459</v>
+      </c>
+      <c r="B19" t="s">
         <v>458</v>
-      </c>
-      <c r="B19" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23">
@@ -51269,55 +51272,55 @@
         <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B24" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B28" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
